--- a/output_files/核心能力與教育目標分析/大學部_核心能力與教育目標達成度分析_20260423.xlsx
+++ b/output_files/核心能力與教育目標分析/大學部_核心能力與教育目標達成度分析_20260423.xlsx
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>計算機概論[73.1], 計算機程式[81.2], 計算機程式[84.1], 計算機程式[80.2], 數位系統設計[75.5], 數位系統設計[79.4], 數位系統設計[70.7], 電工實驗（一）[74.2], 電工實驗（一）[75.9], 電工實驗（一）[69.2], 電子學（一）[77.3], 電子學（一）[73.9], 電子學（一）[60.5], 矩陣理論及應用[86.5], 資料結構[88.2], 電路學（二）[70.1], 電路學（二）[68.5], 電路學（二）[73.8], 電力電子學[77.9], 電磁學（一）[83.2], 電磁學（一）[74.1], 電磁學（一）[64.9], 訊號與系統[82.8], 訊號與系統[76.7], 訊號與系統[74.0], 硬體描述語言[87.3], 電工實驗（三）[86.1], 電工實驗（三）[87.2], 電工實驗（三）[81.0], 電工實驗（五）[89.1], 電工實驗（五）[85.4], 電工實驗（五）[84.3], 電子學（三）[79.5], 半導體元件（一）[80.2], 半導體元件（一）[77.8], 奈微系統工程原理[80.5], 控制系統[64.4], 控制系統[66.9], 控制系統[66.1], 複變函數[65.0], 作業系統[82.7], 無人載具概論[88.3], 電力系統（一）[65.5], 電力系統（一）[92.3], 微波工程[91.3], 無線功率傳輸系統[80.0], 通訊系統[75.8], 通訊系統[82.7], 通訊系統[75.6], 實用數位系統設計[85.4], 數值運算實務[93.1], 天線工程概論[74.0], 數位訊號處理導論[88.8], 機率模式與應用[71.4], 生醫工程導論[81.4], 電機工程進階實作專案[86.2]</t>
+          <t>計算機概論[73.1], 計算機程式[81.2,84.1,80.2], 數位系統設計[75.5,79.4,70.7], 電工實驗（一）[74.2,75.9,69.2], 電子學（一）[77.3,73.9,60.5], 矩陣理論及應用[86.5], 資料結構[88.2], 電路學（二）[70.1,68.5,73.8], 電力電子學[77.9], 電磁學（一）[83.2,74.1,64.9], 訊號與系統[82.8,76.7,74.0], 硬體描述語言[87.3], 電工實驗（三）[86.1,87.2,81.0], 電工實驗（五）[89.1,85.4,84.3], 電子學（三）[79.5], 半導體元件（一）[80.2,77.8], 奈微系統工程原理[80.5], 控制系統[64.4,66.9,66.1], 複變函數[65.0], 作業系統[82.7], 無人載具概論[88.3], 電力系統（一）[65.5,92.3], 微波工程[91.3], 無線功率傳輸系統[80.0], 通訊系統[75.8,82.7,75.6], 實用數位系統設計[85.4], 數值運算實務[93.1], 天線工程概論[74.0], 數位訊號處理導論[88.8], 機率模式與應用[71.4], 生醫工程導論[81.4], 電機工程進階實作專案[86.2]</t>
         </is>
       </c>
       <c r="C2" s="8" t="n">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>微積分（一）[85.5], 微積分（一）[85.6], 微積分（一）[79.8], 計算機概論[83.0], 計算機概論[86.3], 計算機概論[73.1], 計算機程式[81.2], 計算機程式[84.1], 計算機程式[80.2], 數位系統設計[75.5], 數位系統設計[79.4], 數位系統設計[70.7], 電工實驗（一）[74.2], 電工實驗（一）[75.9], 電工實驗（一）[69.2], 電子學（一）[77.3], 電子學（一）[73.9], 電子學（一）[60.5], 矩陣理論及應用[86.5], 資料結構[88.2], 電路學（二）[70.1], 電路學（二）[68.5], 電路學（二）[73.8], 電力電子學[77.9], 電磁學（一）[83.2], 電磁學（一）[74.1], 電磁學（一）[64.9], 訊號與系統[82.8], 訊號與系統[76.7], 訊號與系統[74.0], 硬體描述語言[87.3], 電工實驗（三）[86.1], 電工實驗（三）[87.2], 電工實驗（三）[81.0], 電工實驗（五）[89.1], 電工實驗（五）[85.4], 電工實驗（五）[84.3], 電子學（三）[79.5], 半導體元件（一）[80.2], 半導體元件（一）[77.8], 奈微系統工程原理[80.5], 控制系統[64.4], 控制系統[66.9], 控制系統[66.1], 複變函數[65.0], 作業系統[82.7], 無人載具概論[88.3], 電力系統（一）[65.5], 電力系統（一）[92.3], 微波工程[91.3], 無線功率傳輸系統[80.0], 通訊系統[75.8], 通訊系統[82.7], 通訊系統[75.6], 實用數位系統設計[85.4], 天線工程概論[74.0], 數位訊號處理導論[88.8], 機率模式與應用[71.4], 生醫工程導論[81.4], 電機工程進階實作專案[86.2]</t>
+          <t>微積分（一）[85.5,85.6,79.8], 計算機概論[83.0,86.3,73.1], 計算機程式[81.2,84.1,80.2], 數位系統設計[75.5,79.4,70.7], 電工實驗（一）[74.2,75.9,69.2], 電子學（一）[77.3,73.9,60.5], 矩陣理論及應用[86.5], 資料結構[88.2], 電路學（二）[70.1,68.5,73.8], 電力電子學[77.9], 電磁學（一）[83.2,74.1,64.9], 訊號與系統[82.8,76.7,74.0], 硬體描述語言[87.3], 電工實驗（三）[86.1,87.2,81.0], 電工實驗（五）[89.1,85.4,84.3], 電子學（三）[79.5], 半導體元件（一）[80.2,77.8], 奈微系統工程原理[80.5], 控制系統[64.4,66.9,66.1], 複變函數[65.0], 作業系統[82.7], 無人載具概論[88.3], 電力系統（一）[65.5,92.3], 微波工程[91.3], 無線功率傳輸系統[80.0], 通訊系統[75.8,82.7,75.6], 實用數位系統設計[85.4], 天線工程概論[74.0], 數位訊號處理導論[88.8], 機率模式與應用[71.4], 生醫工程導論[81.4], 電機工程進階實作專案[86.2]</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>計算機概論[83.0], 計算機概論[73.1], 計算機程式[81.2], 計算機程式[84.1], 計算機程式[80.2], 數位系統設計[75.5], 數位系統設計[79.4], 數位系統設計[70.7], 電工實驗（一）[74.2], 電工實驗（一）[75.9], 電工實驗（一）[69.2], 資料結構[88.2], 電路學（二）[70.1], 電路學（二）[68.5], 電力電子學[77.9], 電磁學（一）[64.9], 電工實驗（三）[86.1], 電工實驗（三）[87.2], 電工實驗（三）[81.0], 電工實驗（五）[89.1], 電工實驗（五）[85.4], 電工實驗（五）[84.3], 半導體元件（一）[80.2], 半導體元件（一）[77.8], 奈微系統工程原理[80.5], 無人載具概論[88.3], 微波工程[91.3], 無線功率傳輸系統[80.0], 通訊系統[75.8], 通訊系統[82.7], 通訊系統[75.6], 實用數位系統設計[85.4], 數值運算實務[93.1], 電機工程進階實作專案[86.2]</t>
+          <t>計算機概論[83.0,73.1], 計算機程式[81.2,84.1,80.2], 數位系統設計[75.5,79.4,70.7], 電工實驗（一）[74.2,75.9,69.2], 資料結構[88.2], 電路學（二）[70.1,68.5], 電力電子學[77.9], 電磁學（一）[64.9], 電工實驗（三）[86.1,87.2,81.0], 電工實驗（五）[89.1,85.4,84.3], 半導體元件（一）[80.2,77.8], 奈微系統工程原理[80.5], 無人載具概論[88.3], 微波工程[91.3], 無線功率傳輸系統[80.0], 通訊系統[75.8,82.7,75.6], 實用數位系統設計[85.4], 數值運算實務[93.1], 電機工程進階實作專案[86.2]</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>微積分（一）[85.5], 微積分（一）[85.6], 微積分（一）[79.8], 計算機概論[83.0], 計算機概論[86.3], 計算機程式[81.2], 計算機程式[84.1], 計算機程式[80.2], 數位系統設計[75.5], 數位系統設計[79.4], 數位系統設計[70.7], 電子學（一）[77.3], 電子學（一）[73.9], 矩陣理論及應用[86.5], 資料結構[88.2], 電力電子學[77.9], 硬體描述語言[87.3], 電工實驗（三）[86.1], 電工實驗（三）[87.2], 電工實驗（三）[81.0], 電子學（三）[79.5], 複變函數[65.0], 電力系統（一）[92.3], 無線功率傳輸系統[80.0], 實用數位系統設計[85.4], 數值運算實務[93.1], 天線工程概論[74.0], 機率模式與應用[71.4], 電機工程進階實作專案[86.2]</t>
+          <t>微積分（一）[85.5,85.6,79.8], 計算機概論[83.0,86.3], 計算機程式[81.2,84.1,80.2], 數位系統設計[75.5,79.4,70.7], 電子學（一）[77.3,73.9], 矩陣理論及應用[86.5], 資料結構[88.2], 電力電子學[77.9], 硬體描述語言[87.3], 電工實驗（三）[86.1,87.2,81.0], 電子學（三）[79.5], 複變函數[65.0], 電力系統（一）[92.3], 無線功率傳輸系統[80.0], 實用數位系統設計[85.4], 數值運算實務[93.1], 天線工程概論[74.0], 機率模式與應用[71.4], 電機工程進階實作專案[86.2]</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>計算機概論[86.3], 計算機程式[81.2], 計算機程式[84.1], 計算機程式[80.2], 數位系統設計[75.5], 數位系統設計[79.4], 數位系統設計[70.7], 電路學（二）[70.1], 電路學（二）[68.5], 硬體描述語言[87.3], 電子學（三）[79.5], 半導體元件（一）[80.2], 半導體元件（一）[77.8], 奈微系統工程原理[80.5], 控制系統[64.4], 控制系統[66.9], 無人載具概論[88.3], 電力系統（一）[65.5], 微波工程[91.3], 無線功率傳輸系統[80.0], 通訊系統[75.8], 通訊系統[82.7], 通訊系統[75.6], 天線工程概論[74.0], 生醫工程導論[81.4]</t>
+          <t>計算機概論[86.3], 計算機程式[81.2,84.1,80.2], 數位系統設計[75.5,79.4,70.7], 電路學（二）[70.1,68.5], 硬體描述語言[87.3], 電子學（三）[79.5], 半導體元件（一）[80.2,77.8], 奈微系統工程原理[80.5], 控制系統[64.4,66.9], 無人載具概論[88.3], 電力系統（一）[65.5], 微波工程[91.3], 無線功率傳輸系統[80.0], 通訊系統[75.8,82.7,75.6], 天線工程概論[74.0], 生醫工程導論[81.4]</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>微分方程[71.6], 微分方程[71.2], 微分方程[65.0], 電工實驗（二）[85.9], 電工實驗（二）[85.6], 電工實驗（二）[85.7], 電子學（二）[73.4], 電子學（二）[67.9], 電子學（二）[60.8], 線性代數[67.4], 線性代數[66.8], 線性代數[50.5], 電路學（一）[65.1], 電路學（一）[66.4], 電路學（一）[49.0], 電力電子學[79.2], 電力電子實驗[88.7], 嵌入式軟體設計[86.9], 計算機組織[93.0], 音頻電路設計[68.1], 離散數學[79.7], 離散數學[80.0], 離散數學[78.8], 基礎機器人應用[86.9], 電機機械[75.5], 電機機械[64.6], 電機機械[78.6], 電磁學（二）[71.6], 電磁學（二）[65.4], 電磁學（二）[65.8], 微波元件導論[89.3], 機率與統計[82.2], 機率與統計[82.8], 機率與統計[71.8], ＶＬＳＩ設計導論[87.0], ＶＬＳＩ設計導論[86.0], 實用數位系統設計[87.5], 生醫訊號處理與儀器實作專題[91.8], 生醫訊號處理與儀器實作專題[90.4], 生醫訊號處理與儀器實作專題[95.0], 電工實驗（四）[83.2], 電工實驗（四）[85.8], 電工實驗（四）[82.4], 半導體元件（二）[81.4], 半導體元件（二）[83.1], 微電子技術[85.8], 微電子技術[78.7], 資訊安全概論[78.3], 無線通訊系統導論[95.0], 電子實作專題[91.1], 電子實作專題[95.0], 電子實作專題[92.5], 計算機實作專題[70.6], 計算機實作專題[88.5], 計算機實作專題[84.1], 電力實作專題[75.0], 電力實作專題[93.0], 電波與光電實作專題[91.0], 電波與光電實作專題[87.0], 通訊實作專題[81.1], 通訊實作專題[89.4], 通訊實作專題[80.1], 系統晶片實作專題[89.2], 系統晶片實作專題[91.4], 系統晶片實作專題[90.9]</t>
+          <t>微分方程[71.6,71.2,65.0], 電工實驗（二）[85.9,85.6,85.7], 電子學（二）[73.4,67.9,60.8], 線性代數[67.4,66.8,50.5], 電路學（一）[65.1,66.4,49.0], 電力電子學[79.2], 電力電子實驗[88.7], 嵌入式軟體設計[86.9], 計算機組織[93.0], 音頻電路設計[68.1], 離散數學[79.7,80.0,78.8], 基礎機器人應用[86.9], 電機機械[75.5,64.6,78.6], 電磁學（二）[71.6,65.4,65.8], 微波元件導論[89.3], 機率與統計[82.2,82.8,71.8], ＶＬＳＩ設計導論[87.0,86.0], 實用數位系統設計[87.5], 生醫訊號處理與儀器實作專題[91.8,90.4,95.0], 電工實驗（四）[83.2,85.8,82.4], 半導體元件（二）[81.4,83.1], 微電子技術[85.8,78.7], 資訊安全概論[78.3], 無線通訊系統導論[95.0], 電子實作專題[91.1,95.0,92.5], 計算機實作專題[70.6,88.5,84.1], 電力實作專題[75.0,93.0], 電波與光電實作專題[91.0,87.0], 通訊實作專題[81.1,89.4,80.1], 系統晶片實作專題[89.2,91.4,90.9]</t>
         </is>
       </c>
       <c r="C2" s="8" t="n">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>微積分（二）[85.7], 微積分（二）[82.8], 微積分（二）[75.1], 微分方程[71.6], 微分方程[71.2], 微分方程[65.0], 電工實驗（二）[85.9], 電工實驗（二）[85.6], 電工實驗（二）[85.7], 電子學（二）[73.4], 電子學（二）[67.9], 線性代數[67.4], 線性代數[66.8], 線性代數[50.5], 電路學（一）[65.1], 電路學（一）[66.4], 電路學（一）[49.0], 電力電子學[79.2], 電力電子實驗[88.7], 計算機組織[93.0], 離散數學[78.8], 基礎機器人應用[86.9], 電機機械[75.5], 電機機械[64.6], 電機機械[78.6], 電磁學（二）[65.8], 微波元件導論[89.3], 機率與統計[82.2], 機率與統計[82.8], 機率與統計[71.8], ＶＬＳＩ設計導論[86.0], 實用數位系統設計[87.5], 生醫訊號處理與儀器實作專題[91.8], 生醫訊號處理與儀器實作專題[95.0], 半導體元件（二）[81.4], 半導體元件（二）[83.1], 微電子技術[85.8], 資訊安全概論[78.3], 無線通訊系統導論[95.0], 電子實作專題[91.1], 電子實作專題[95.0], 電子實作專題[92.5], 計算機實作專題[70.6], 計算機實作專題[88.5], 計算機實作專題[84.1], 電力實作專題[75.0], 電力實作專題[93.0], 電波與光電實作專題[91.0], 電波與光電實作專題[87.0], 通訊實作專題[81.1], 通訊實作專題[89.4], 通訊實作專題[80.1], 系統晶片實作專題[89.2], 系統晶片實作專題[91.4], 系統晶片實作專題[90.9]</t>
+          <t>微積分（二）[85.7,82.8,75.1], 微分方程[71.6,71.2,65.0], 電工實驗（二）[85.9,85.6,85.7], 電子學（二）[73.4,67.9], 線性代數[67.4,66.8,50.5], 電路學（一）[65.1,66.4,49.0], 電力電子學[79.2], 電力電子實驗[88.7], 計算機組織[93.0], 離散數學[78.8], 基礎機器人應用[86.9], 電機機械[75.5,64.6,78.6], 電磁學（二）[65.8], 微波元件導論[89.3], 機率與統計[82.2,82.8,71.8], ＶＬＳＩ設計導論[86.0], 實用數位系統設計[87.5], 生醫訊號處理與儀器實作專題[91.8,95.0], 半導體元件（二）[81.4,83.1], 微電子技術[85.8], 資訊安全概論[78.3], 無線通訊系統導論[95.0], 電子實作專題[91.1,95.0,92.5], 計算機實作專題[70.6,88.5,84.1], 電力實作專題[75.0,93.0], 電波與光電實作專題[91.0,87.0], 通訊實作專題[81.1,89.4,80.1], 系統晶片實作專題[89.2,91.4,90.9]</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>微積分（二）[82.8], 微積分（二）[75.1], 電工實驗（二）[85.9], 電工實驗（二）[85.6], 電工實驗（二）[85.7], 線性代數[67.4], 電路學（一）[49.0], 電力電子學[79.2], 電力電子實驗[88.7], 離散數學[78.8], 基礎機器人應用[86.9], 機率與統計[71.8], ＶＬＳＩ設計導論[86.0], 實用數位系統設計[87.5], 生醫訊號處理與儀器實作專題[91.8], 生醫訊號處理與儀器實作專題[95.0], 半導體元件（二）[81.4], 半導體元件（二）[83.1], 微電子技術[85.8], 電子實作專題[91.1], 電子實作專題[95.0], 電子實作專題[92.5], 計算機實作專題[70.6], 計算機實作專題[88.5], 計算機實作專題[84.1], 電力實作專題[75.0], 電力實作專題[93.0], 電波與光電實作專題[91.0], 電波與光電實作專題[87.0], 通訊實作專題[81.1], 通訊實作專題[89.4], 通訊實作專題[80.1], 系統晶片實作專題[89.2], 系統晶片實作專題[91.4], 系統晶片實作專題[90.9]</t>
+          <t>微積分（二）[82.8,75.1], 電工實驗（二）[85.9,85.6,85.7], 線性代數[67.4], 電路學（一）[49.0], 電力電子學[79.2], 電力電子實驗[88.7], 離散數學[78.8], 基礎機器人應用[86.9], 機率與統計[71.8], ＶＬＳＩ設計導論[86.0], 實用數位系統設計[87.5], 生醫訊號處理與儀器實作專題[91.8,95.0], 半導體元件（二）[81.4,83.1], 微電子技術[85.8], 電子實作專題[91.1,95.0,92.5], 計算機實作專題[70.6,88.5,84.1], 電力實作專題[75.0,93.0], 電波與光電實作專題[91.0,87.0], 通訊實作專題[81.1,89.4,80.1], 系統晶片實作專題[89.2,91.4,90.9]</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>微積分（二）[85.7], 電子學（二）[73.4], 電子學（二）[67.9], 電路學（一）[49.0], 計算機組織[93.0], 音頻電路設計[68.1], 離散數學[78.8], 基礎機器人應用[86.9], 電機機械[75.5], 電機機械[64.6], 電機機械[78.6], 機率與統計[82.2], 機率與統計[82.8], 機率與統計[71.8], ＶＬＳＩ設計導論[86.0], 實用數位系統設計[87.5], 資訊安全概論[78.3], 無線通訊系統導論[95.0]</t>
+          <t>微積分（二）[85.7], 電子學（二）[73.4,67.9], 電路學（一）[49.0], 計算機組織[93.0], 音頻電路設計[68.1], 離散數學[78.8], 基礎機器人應用[86.9], 電機機械[75.5,64.6,78.6], 機率與統計[82.2,82.8,71.8], ＶＬＳＩ設計導論[86.0], 實用數位系統設計[87.5], 資訊安全概論[78.3], 無線通訊系統導論[95.0]</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>電子學（二）[73.4], 電子學（二）[67.9], 線性代數[67.4], 線性代數[66.8], 電路學（一）[65.1], 電路學（一）[66.4], 電力電子學[79.2], 計算機組織[93.0], 音頻電路設計[68.1], 基礎機器人應用[86.9], 電機機械[75.5], 電機機械[64.6], 電機機械[78.6], 半導體元件（二）[81.4], 半導體元件（二）[83.1], 微電子技術[85.8]</t>
+          <t>電子學（二）[73.4,67.9], 線性代數[67.4,66.8], 電路學（一）[65.1,66.4], 電力電子學[79.2], 計算機組織[93.0], 音頻電路設計[68.1], 基礎機器人應用[86.9], 電機機械[75.5,64.6,78.6], 半導體元件（二）[81.4,83.1], 微電子技術[85.8]</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>計算機概論[86.4], 計算機程式[86.5], 計算機程式[82.8], 計算機程式[83.9], 數位系統設計[85.6], 數位系統設計[82.8], 數位系統設計[73.1], 電工實驗（一）[72.6], 電工實驗（一）[71.5], 電工實驗（一）[73.0], 電子學（一）[71.0], 電子學（一）[65.4], 電子學（一）[73.5], 矩陣理論及應用[95.0], 矩陣理論及應用[85.0], 資料結構[78.3], 電路學（二）[64.2], 電路學（二）[62.7], 電路學（二）[69.2], 電力電子學[76.8], 電磁學（一）[67.7], 電磁學（一）[70.4], 電磁學（一）[60.4], 訊號與系統[76.1], 訊號與系統[73.9], 訊號與系統[72.5], 硬體描述語言[91.8], 電工實驗（三）[90.0], 電工實驗（三）[86.7], 電工實驗（三）[81.0], 電工實驗（五）[90.1], 電工實驗（五）[92.8], 電工實驗（五）[89.6], 電子學（三）[81.9], 半導體元件（一）[85.9], 半導體元件（一）[80.6], 電子材料工程[75.8], 控制系統[80.2], 控制系統[79.3], 控制系統[78.2], 無人載具概論[93.8], 電力系統（一）[77.0], 電力系統（一）[68.0], 微波工程[85.3], 通訊系統[77.4], 通訊系統[72.7], 通訊系統[63.7], 實用數位系統設計[86.4], 數值運算實務[90.9], 資訊安全概論[84.5], 天線工程概論[66.6], 數位訊號處理導論[86.2], 機率模式與應用[84.2], 生醫工程導論[77.6], 電機工程進階實作專案[91.6]</t>
+          <t>計算機概論[86.4], 計算機程式[86.5,82.8,83.9], 數位系統設計[85.6,82.8,73.1], 電工實驗（一）[72.6,71.5,73.0], 電子學（一）[71.0,65.4,73.5], 矩陣理論及應用[95.0,85.0], 資料結構[78.3], 電路學（二）[64.2,62.7,69.2], 電力電子學[76.8], 電磁學（一）[67.7,70.4,60.4], 訊號與系統[76.1,73.9,72.5], 硬體描述語言[91.8], 電工實驗（三）[90.0,86.7,81.0], 電工實驗（五）[90.1,92.8,89.6], 電子學（三）[81.9], 半導體元件（一）[85.9,80.6], 電子材料工程[75.8], 控制系統[80.2,79.3,78.2], 無人載具概論[93.8], 電力系統（一）[77.0,68.0], 微波工程[85.3], 通訊系統[77.4,72.7,63.7], 實用數位系統設計[86.4], 數值運算實務[90.9], 資訊安全概論[84.5], 天線工程概論[66.6], 數位訊號處理導論[86.2], 機率模式與應用[84.2], 生醫工程導論[77.6], 電機工程進階實作專案[91.6]</t>
         </is>
       </c>
       <c r="C2" s="8" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>微積分（一）[82.3], 微積分（一）[76.6], 微積分（一）[79.6], 計算機概論[82.3], 計算機概論[83.1], 計算機概論[86.4], 計算機程式[86.5], 計算機程式[82.8], 計算機程式[83.9], 數位系統設計[85.6], 數位系統設計[82.8], 數位系統設計[73.1], 電工實驗（一）[72.6], 電工實驗（一）[71.5], 電工實驗（一）[73.0], 電子學（一）[71.0], 電子學（一）[65.4], 電子學（一）[73.5], 矩陣理論及應用[95.0], 矩陣理論及應用[85.0], 資料結構[78.3], 電路學（二）[64.2], 電路學（二）[62.7], 電路學（二）[69.2], 電力電子學[76.8], 電磁學（一）[67.7], 電磁學（一）[70.4], 電磁學（一）[60.4], 訊號與系統[76.1], 訊號與系統[73.9], 訊號與系統[72.5], 硬體描述語言[91.8], 電工實驗（三）[90.0], 電工實驗（三）[86.7], 電工實驗（三）[81.0], 電工實驗（五）[90.1], 電工實驗（五）[92.8], 電工實驗（五）[89.6], 電子學（三）[81.9], 半導體元件（一）[85.9], 半導體元件（一）[80.6], 電子材料工程[75.8], 控制系統[80.2], 控制系統[79.3], 控制系統[78.2], 無人載具概論[93.8], 電力系統（一）[77.0], 電力系統（一）[68.0], 微波工程[85.3], 通訊系統[77.4], 通訊系統[72.7], 通訊系統[63.7], 實用數位系統設計[86.4], 資訊安全概論[84.5], 天線工程概論[66.6], 數位訊號處理導論[86.2], 機率模式與應用[84.2], 生醫工程導論[77.6], 電機工程進階實作專案[91.6]</t>
+          <t>微積分（一）[82.3,76.6,79.6], 計算機概論[82.3,83.1,86.4], 計算機程式[86.5,82.8,83.9], 數位系統設計[85.6,82.8,73.1], 電工實驗（一）[72.6,71.5,73.0], 電子學（一）[71.0,65.4,73.5], 矩陣理論及應用[95.0,85.0], 資料結構[78.3], 電路學（二）[64.2,62.7,69.2], 電力電子學[76.8], 電磁學（一）[67.7,70.4,60.4], 訊號與系統[76.1,73.9,72.5], 硬體描述語言[91.8], 電工實驗（三）[90.0,86.7,81.0], 電工實驗（五）[90.1,92.8,89.6], 電子學（三）[81.9], 半導體元件（一）[85.9,80.6], 電子材料工程[75.8], 控制系統[80.2,79.3,78.2], 無人載具概論[93.8], 電力系統（一）[77.0,68.0], 微波工程[85.3], 通訊系統[77.4,72.7,63.7], 實用數位系統設計[86.4], 資訊安全概論[84.5], 天線工程概論[66.6], 數位訊號處理導論[86.2], 機率模式與應用[84.2], 生醫工程導論[77.6], 電機工程進階實作專案[91.6]</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>計算機概論[82.3], 計算機概論[83.1], 計算機概論[86.4], 計算機程式[86.5], 計算機程式[82.8], 計算機程式[83.9], 數位系統設計[85.6], 數位系統設計[82.8], 數位系統設計[73.1], 電工實驗（一）[72.6], 電工實驗（一）[71.5], 電工實驗（一）[73.0], 資料結構[78.3], 電路學（二）[64.2], 電路學（二）[62.7], 電力電子學[76.8], 電磁學（一）[60.4], 電工實驗（三）[90.0], 電工實驗（三）[86.7], 電工實驗（三）[81.0], 電工實驗（五）[90.1], 電工實驗（五）[92.8], 電工實驗（五）[89.6], 半導體元件（一）[85.9], 半導體元件（一）[80.6], 無人載具概論[93.8], 電力系統（一）[77.0], 微波工程[85.3], 通訊系統[77.4], 通訊系統[72.7], 通訊系統[63.7], 實用數位系統設計[86.4], 數值運算實務[90.9], 資訊安全概論[84.5], 電機工程進階實作專案[91.6]</t>
+          <t>計算機概論[82.3,83.1,86.4], 計算機程式[86.5,82.8,83.9], 數位系統設計[85.6,82.8,73.1], 電工實驗（一）[72.6,71.5,73.0], 資料結構[78.3], 電路學（二）[64.2,62.7], 電力電子學[76.8], 電磁學（一）[60.4], 電工實驗（三）[90.0,86.7,81.0], 電工實驗（五）[90.1,92.8,89.6], 半導體元件（一）[85.9,80.6], 無人載具概論[93.8], 電力系統（一）[77.0], 微波工程[85.3], 通訊系統[77.4,72.7,63.7], 實用數位系統設計[86.4], 數值運算實務[90.9], 資訊安全概論[84.5], 電機工程進階實作專案[91.6]</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>微積分（一）[82.3], 微積分（一）[76.6], 微積分（一）[79.6], 計算機概論[82.3], 計算機概論[83.1], 計算機程式[86.5], 計算機程式[82.8], 計算機程式[83.9], 數位系統設計[85.6], 數位系統設計[82.8], 電子學（一）[71.0], 電子學（一）[65.4], 矩陣理論及應用[85.0], 資料結構[78.3], 電路學（二）[69.2], 電力電子學[76.8], 電磁學（一）[60.4], 硬體描述語言[91.8], 電工實驗（三）[90.0], 電工實驗（三）[86.7], 電工實驗（三）[81.0], 電子學（三）[81.9], 電力系統（一）[68.0], 實用數位系統設計[86.4], 數值運算實務[90.9], 資訊安全概論[84.5], 天線工程概論[66.6], 機率模式與應用[84.2], 電機工程進階實作專案[91.6]</t>
+          <t>微積分（一）[82.3,76.6,79.6], 計算機概論[82.3,83.1], 計算機程式[86.5,82.8,83.9], 數位系統設計[85.6,82.8], 電子學（一）[71.0,65.4], 矩陣理論及應用[85.0], 資料結構[78.3], 電路學（二）[69.2], 電力電子學[76.8], 電磁學（一）[60.4], 硬體描述語言[91.8], 電工實驗（三）[90.0,86.7,81.0], 電子學（三）[81.9], 電力系統（一）[68.0], 實用數位系統設計[86.4], 數值運算實務[90.9], 資訊安全概論[84.5], 天線工程概論[66.6], 機率模式與應用[84.2], 電機工程進階實作專案[91.6]</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>計算機程式[86.5], 計算機程式[82.8], 計算機程式[83.9], 數位系統設計[85.6], 數位系統設計[82.8], 數位系統設計[73.1], 電路學（二）[64.2], 電路學（二）[62.7], 電路學（二）[69.2], 硬體描述語言[91.8], 電子學（三）[81.9], 半導體元件（一）[85.9], 半導體元件（一）[80.6], 電子材料工程[75.8], 控制系統[80.2], 控制系統[79.3], 無人載具概論[93.8], 電力系統（一）[77.0], 微波工程[85.3], 通訊系統[77.4], 通訊系統[72.7], 通訊系統[63.7], 天線工程概論[66.6], 生醫工程導論[77.6]</t>
+          <t>計算機程式[86.5,82.8,83.9], 數位系統設計[85.6,82.8,73.1], 電路學（二）[64.2,62.7,69.2], 硬體描述語言[91.8], 電子學（三）[81.9], 半導體元件（一）[85.9,80.6], 電子材料工程[75.8], 控制系統[80.2,79.3], 無人載具概論[93.8], 電力系統（一）[77.0], 微波工程[85.3], 通訊系統[77.4,72.7,63.7], 天線工程概論[66.6], 生醫工程導論[77.6]</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>微積分（一）[79.1], 微積分（一）[65.3], 計算機概論[88.7], 計算機概論[88.1], 數位系統設計[78.0], 數位系統設計[72.6], 電工實驗（一）[79.0], 電子學（一）[65.2], 電子學（一）[73.4], 資料結構[78.2], 電路學（二）[65.3], 電路學（二）[70.2], 電磁學（一）[85.3], 電磁學（一）[63.8], 訊號與系統[71.7], 訊號與系統[76.7], 電工實驗（三）[84.4], 電工實驗（三）[83.8], 電工實驗（五）[87.7], 電工實驗（五）[84.8], 電子學（三）[79.3], 半導體元件（一）[78.0], 奈微系統工程原理[83.5], 電子材料工程[74.1], 控制系統[61.7], 控制系統[63.5], 複變函數[67.9], 複變函數[81.4], 資料探勘導論[77.9], 影像通訊[75.0], 電力系統（一）[72.3], 工程經濟[73.9], 微波工程[81.1], 通訊系統[69.7], 通訊系統[76.0], 機器學習系統設計實務與應用[90.2], 微電子技術[78.4], 線性系統概論[87.0], 數位訊號處理導論[72.0], 機率模式與應用[74.3], 智慧物聯網系統設計實務[90.1], 電機工程進階實作專案[93.9]</t>
+          <t>微積分（一）[79.1,65.3], 計算機概論[88.7,88.1], 數位系統設計[78.0,72.6], 電工實驗（一）[79.0], 電子學（一）[65.2,73.4], 資料結構[78.2], 電路學（二）[65.3,70.2], 電磁學（一）[85.3,63.8], 訊號與系統[71.7,76.7], 電工實驗（三）[84.4,83.8], 電工實驗（五）[87.7,84.8], 電子學（三）[79.3], 半導體元件（一）[78.0], 奈微系統工程原理[83.5], 電子材料工程[74.1], 控制系統[61.7,63.5], 複變函數[67.9,81.4], 資料探勘導論[77.9], 影像通訊[75.0], 電力系統（一）[72.3], 工程經濟[73.9], 微波工程[81.1], 通訊系統[69.7,76.0], 機器學習系統設計實務與應用[90.2], 微電子技術[78.4], 線性系統概論[87.0], 數位訊號處理導論[72.0], 機率模式與應用[74.3], 智慧物聯網系統設計實務[90.1], 電機工程進階實作專案[93.9]</t>
         </is>
       </c>
       <c r="C2" s="8" t="n">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>微積分（一）[79.1], 微積分（一）[65.3], 計算機概論[88.7], 計算機概論[88.1], 計算機程式[74.1], 計算機程式[77.0], 數位系統設計[78.0], 數位系統設計[72.6], 電工實驗（一）[79.0], 電子學（一）[65.2], 電子學（一）[73.4], 資料結構[78.2], 電路學（二）[65.3], 電路學（二）[70.2], 電磁學（一）[85.3], 訊號與系統[71.7], 訊號與系統[76.7], 硬體描述語言[80.8], 電工實驗（三）[84.4], 電工實驗（三）[83.8], 電工實驗（五）[84.8], 電子學（三）[79.3], 半導體元件（一）[78.0], 奈微系統工程原理[83.5], 電子材料工程[74.1], 控制系統[61.7], 控制系統[63.5], 複變函數[67.9], 複變函數[81.4], 資料探勘導論[77.9], 影像通訊[75.0], 電力系統（一）[72.3], 工程經濟[73.9], 微波工程[81.1], 通訊系統[69.7], 通訊系統[76.0], 機器學習系統設計實務與應用[90.2], 微電子技術[78.4], 線性系統概論[87.0], 數位訊號處理導論[72.0], 數位通訊[87.1], 機率模式與應用[74.3], 智慧物聯網系統設計實務[90.1], 電機工程進階實作專案[93.9]</t>
+          <t>微積分（一）[79.1,65.3], 計算機概論[88.7,88.1], 計算機程式[74.1,77.0], 數位系統設計[78.0,72.6], 電工實驗（一）[79.0], 電子學（一）[65.2,73.4], 資料結構[78.2], 電路學（二）[65.3,70.2], 電磁學（一）[85.3], 訊號與系統[71.7,76.7], 硬體描述語言[80.8], 電工實驗（三）[84.4,83.8], 電工實驗（五）[84.8], 電子學（三）[79.3], 半導體元件（一）[78.0], 奈微系統工程原理[83.5], 電子材料工程[74.1], 控制系統[61.7,63.5], 複變函數[67.9,81.4], 資料探勘導論[77.9], 影像通訊[75.0], 電力系統（一）[72.3], 工程經濟[73.9], 微波工程[81.1], 通訊系統[69.7,76.0], 機器學習系統設計實務與應用[90.2], 微電子技術[78.4], 線性系統概論[87.0], 數位訊號處理導論[72.0], 數位通訊[87.1], 機率模式與應用[74.3], 智慧物聯網系統設計實務[90.1], 電機工程進階實作專案[93.9]</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>微積分（一）[79.1], 微積分（一）[65.3], 計算機概論[88.7], 計算機概論[88.1], 計算機程式[74.1], 計算機程式[77.0], 數位系統設計[78.0], 數位系統設計[72.6], 電工實驗（一）[79.0], 電子學（一）[65.2], 電子學（一）[73.4], 電路學（二）[65.3], 硬體描述語言[80.8], 電工實驗（三）[84.4], 電工實驗（三）[83.8], 電工實驗（五）[84.8], 半導體元件（一）[78.0], 奈微系統工程原理[83.5], 控制系統[61.7], 控制系統[63.5], 資料探勘導論[77.9], 影像通訊[75.0], 工程經濟[73.9], 通訊系統[69.7], 通訊系統[76.0], 機器學習系統設計實務與應用[90.2], 微電子技術[78.4], 智慧物聯網系統設計實務[90.1], 電機工程進階實作專案[93.9]</t>
+          <t>微積分（一）[79.1,65.3], 計算機概論[88.7,88.1], 計算機程式[74.1,77.0], 數位系統設計[78.0,72.6], 電工實驗（一）[79.0], 電子學（一）[65.2,73.4], 電路學（二）[65.3], 硬體描述語言[80.8], 電工實驗（三）[84.4,83.8], 電工實驗（五）[84.8], 半導體元件（一）[78.0], 奈微系統工程原理[83.5], 控制系統[61.7,63.5], 資料探勘導論[77.9], 影像通訊[75.0], 工程經濟[73.9], 通訊系統[69.7,76.0], 機器學習系統設計實務與應用[90.2], 微電子技術[78.4], 智慧物聯網系統設計實務[90.1], 電機工程進階實作專案[93.9]</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>微積分（一）[79.1], 計算機程式[74.1], 計算機程式[77.0], 電工實驗（一）[79.0], 電子學（一）[73.4], 資料結構[78.2], 電路學（二）[70.2], 硬體描述語言[80.8], 電工實驗（五）[84.8], 電子學（三）[79.3], 電子材料工程[74.1], 控制系統[63.5], 資料探勘導論[77.9], 影像通訊[75.0], 工程經濟[73.9], 通訊系統[69.7], 機器學習系統設計實務與應用[90.2], 微電子技術[78.4], 線性系統概論[87.0], 機率模式與應用[74.3], 電機工程進階實作專案[93.9]</t>
+          <t>微積分（一）[79.1], 計算機程式[74.1,77.0], 電工實驗（一）[79.0], 電子學（一）[73.4], 資料結構[78.2], 電路學（二）[70.2], 硬體描述語言[80.8], 電工實驗（五）[84.8], 電子學（三）[79.3], 電子材料工程[74.1], 控制系統[63.5], 資料探勘導論[77.9], 影像通訊[75.0], 工程經濟[73.9], 通訊系統[69.7], 機器學習系統設計實務與應用[90.2], 微電子技術[78.4], 線性系統概論[87.0], 機率模式與應用[74.3], 電機工程進階實作專案[93.9]</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>計算機概論[88.7], 計算機概論[88.1], 數位系統設計[72.6], 電子學（一）[65.2], 資料結構[78.2], 電路學（二）[65.3], 電路學（二）[70.2], 電子學（三）[79.3], 半導體元件（一）[78.0], 奈微系統工程原理[83.5], 控制系統[61.7], 資料探勘導論[77.9], 電力系統（一）[72.3], 工程經濟[73.9], 通訊系統[76.0], 微電子技術[78.4], 線性系統概論[87.0], 數位通訊[87.1]</t>
+          <t>計算機概論[88.7,88.1], 數位系統設計[72.6], 電子學（一）[65.2], 資料結構[78.2], 電路學（二）[65.3,70.2], 電子學（三）[79.3], 半導體元件（一）[78.0], 奈微系統工程原理[83.5], 控制系統[61.7], 資料探勘導論[77.9], 電力系統（一）[72.3], 工程經濟[73.9], 通訊系統[76.0], 微電子技術[78.4], 線性系統概論[87.0], 數位通訊[87.1]</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>微積分（二）[85.2], 微積分（二）[68.8], 微分方程[84.6], 微分方程[86.6], 電工實驗（二）[85.3], 電工實驗（二）[87.2], 電子學（二）[65.9], 電子學（二）[67.0], 線性代數[65.2], 線性代數[65.5], 矩陣理論及應用[65.3], 電路學（一）[67.0], 電路學（一）[67.5], 嵌入式軟體設計[77.6], 計算機組織[78.6], 化合物半導體概論[75.7], 音頻電路設計[80.5], 離散數學[76.5], 離散數學[78.6], 類神經網路導論[84.6], 電機機械[69.5], 電機機械[63.8], 電能轉換實作專題[95.0], 電磁學（二）[59.6], 電磁學（二）[58.2], 微波電路實驗[90.0], 機率與統計[75.9], 機率與統計[80.0], 通訊系統模擬[83.6], ＶＬＳＩ設計導論[81.2], 實用數位系統設計[87.0], 數值運算實務[85.0], 電工實驗（四）[86.4], 電工實驗（四）[84.6], 半導體元件（二）[84.1], 微電子技術[84.0], 最佳化簡介[81.0], 電源與電池管理系統導論[78.8], 無線通訊系統導論[69.9], 生醫工程導論[83.4], 智慧物聯網系統設計實務[82.7], 電波與光電實作專題[87.0], 通訊實作專題[82.1]</t>
+          <t>微積分（二）[85.2,68.8], 微分方程[84.6,86.6], 電工實驗（二）[85.3,87.2], 電子學（二）[65.9,67.0], 線性代數[65.2,65.5], 矩陣理論及應用[65.3], 電路學（一）[67.0,67.5], 嵌入式軟體設計[77.6], 計算機組織[78.6], 化合物半導體概論[75.7], 音頻電路設計[80.5], 離散數學[76.5,78.6], 類神經網路導論[84.6], 電機機械[69.5,63.8], 電能轉換實作專題[95.0], 電磁學（二）[59.6,58.2], 微波電路實驗[90.0], 機率與統計[75.9,80.0], 通訊系統模擬[83.6], ＶＬＳＩ設計導論[81.2], 實用數位系統設計[87.0], 數值運算實務[85.0], 電工實驗（四）[86.4,84.6], 半導體元件（二）[84.1], 微電子技術[84.0], 最佳化簡介[81.0], 電源與電池管理系統導論[78.8], 無線通訊系統導論[69.9], 生醫工程導論[83.4], 智慧物聯網系統設計實務[82.7], 電波與光電實作專題[87.0], 通訊實作專題[82.1]</t>
         </is>
       </c>
       <c r="C2" s="8" t="n">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>微積分（二）[85.2], 微積分（二）[68.8], 微分方程[84.6], 微分方程[86.6], 電工實驗（二）[85.3], 電工實驗（二）[87.2], 電子學（二）[65.9], 電子學（二）[67.0], 線性代數[65.2], 線性代數[65.5], 矩陣理論及應用[65.3], 電路學（一）[67.0], 電路學（一）[67.5], 嵌入式軟體設計[77.6], 計算機組織[78.6], 化合物半導體概論[75.7], 音頻電路設計[80.5], 離散數學[76.5], 離散數學[78.6], 類神經網路導論[84.6], 電機機械[69.5], 電機機械[63.8], 電能轉換實作專題[95.0], 電磁學（二）[59.6], 電磁學（二）[58.2], 系統級封裝設計實務[88.9], 微波電路實驗[90.0], 機率與統計[75.9], 機率與統計[80.0], 通訊系統模擬[83.6], ＶＬＳＩ設計導論[81.2], 實用數位系統設計[87.0], 數值運算實務[85.0], 電工實驗（四）[86.4], 電工實驗（四）[84.6], 半導體元件（二）[84.1], 微電子技術[84.0], 最佳化簡介[81.0], 電源與電池管理系統導論[78.8], 無線通訊系統導論[69.9], 生醫工程導論[83.4], 智慧物聯網系統設計實務[82.7], 電波與光電實作專題[87.0], 通訊實作專題[82.1]</t>
+          <t>微積分（二）[85.2,68.8], 微分方程[84.6,86.6], 電工實驗（二）[85.3,87.2], 電子學（二）[65.9,67.0], 線性代數[65.2,65.5], 矩陣理論及應用[65.3], 電路學（一）[67.0,67.5], 嵌入式軟體設計[77.6], 計算機組織[78.6], 化合物半導體概論[75.7], 音頻電路設計[80.5], 離散數學[76.5,78.6], 類神經網路導論[84.6], 電機機械[69.5,63.8], 電能轉換實作專題[95.0], 電磁學（二）[59.6,58.2], 系統級封裝設計實務[88.9], 微波電路實驗[90.0], 機率與統計[75.9,80.0], 通訊系統模擬[83.6], ＶＬＳＩ設計導論[81.2], 實用數位系統設計[87.0], 數值運算實務[85.0], 電工實驗（四）[86.4,84.6], 半導體元件（二）[84.1], 微電子技術[84.0], 最佳化簡介[81.0], 電源與電池管理系統導論[78.8], 無線通訊系統導論[69.9], 生醫工程導論[83.4], 智慧物聯網系統設計實務[82.7], 電波與光電實作專題[87.0], 通訊實作專題[82.1]</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>微積分（二）[85.2], 電工實驗（二）[85.3], 電工實驗（二）[87.2], 電子學（二）[65.9], 線性代數[65.2], 矩陣理論及應用[65.3], 電路學（一）[67.0], 電路學（一）[67.5], 計算機組織[78.6], 電機機械[69.5], 電機機械[63.8], 微波電路實驗[90.0], 通訊系統模擬[83.6], 實用數位系統設計[87.0], 數值運算實務[85.0], 電工實驗（四）[86.4], 電工實驗（四）[84.6], 半導體元件（二）[84.1], 微電子技術[84.0], 最佳化簡介[81.0], 電源與電池管理系統導論[78.8], 智慧物聯網系統設計實務[82.7], 電波與光電實作專題[87.0], 通訊實作專題[82.1]</t>
+          <t>微積分（二）[85.2], 電工實驗（二）[85.3,87.2], 電子學（二）[65.9], 線性代數[65.2], 矩陣理論及應用[65.3], 電路學（一）[67.0,67.5], 計算機組織[78.6], 電機機械[69.5,63.8], 微波電路實驗[90.0], 通訊系統模擬[83.6], 實用數位系統設計[87.0], 數值運算實務[85.0], 電工實驗（四）[86.4,84.6], 半導體元件（二）[84.1], 微電子技術[84.0], 最佳化簡介[81.0], 電源與電池管理系統導論[78.8], 智慧物聯網系統設計實務[82.7], 電波與光電實作專題[87.0], 通訊實作專題[82.1]</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>微積分（二）[85.2], 電子學（二）[65.9], 電子學（二）[67.0], 線性代數[65.2], 矩陣理論及應用[65.3], 電路學（一）[67.5], 嵌入式軟體設計[77.6], 計算機組織[78.6], 離散數學[76.5], 離散數學[78.6], 類神經網路導論[84.6], 電機機械[69.5], 電機機械[63.8], 電能轉換實作專題[95.0], 微波電路實驗[90.0], 機率與統計[75.9], 機率與統計[80.0], 通訊系統模擬[83.6], ＶＬＳＩ設計導論[81.2], 實用數位系統設計[87.0], 數值運算實務[85.0], 電工實驗（四）[86.4], 最佳化簡介[81.0], 電源與電池管理系統導論[78.8], 無線通訊系統導論[69.9], 生醫工程導論[83.4], 智慧物聯網系統設計實務[82.7], 電波與光電實作專題[87.0], 通訊實作專題[82.1]</t>
+          <t>微積分（二）[85.2], 電子學（二）[65.9,67.0], 線性代數[65.2], 矩陣理論及應用[65.3], 電路學（一）[67.5], 嵌入式軟體設計[77.6], 計算機組織[78.6], 離散數學[76.5,78.6], 類神經網路導論[84.6], 電機機械[69.5,63.8], 電能轉換實作專題[95.0], 微波電路實驗[90.0], 機率與統計[75.9,80.0], 通訊系統模擬[83.6], ＶＬＳＩ設計導論[81.2], 實用數位系統設計[87.0], 數值運算實務[85.0], 電工實驗（四）[86.4], 最佳化簡介[81.0], 電源與電池管理系統導論[78.8], 無線通訊系統導論[69.9], 生醫工程導論[83.4], 智慧物聯網系統設計實務[82.7], 電波與光電實作專題[87.0], 通訊實作專題[82.1]</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>電子學（二）[67.0], 矩陣理論及應用[65.3], 電路學（一）[67.5], 音頻電路設計[80.5], 離散數學[76.5], 離散數學[78.6], 類神經網路導論[84.6], 電機機械[69.5], 電機機械[63.8], 電能轉換實作專題[95.0], 系統級封裝設計實務[88.9], ＶＬＳＩ設計導論[81.2], 半導體元件（二）[84.1], 微電子技術[84.0], 最佳化簡介[81.0], 電源與電池管理系統導論[78.8]</t>
+          <t>電子學（二）[67.0], 矩陣理論及應用[65.3], 電路學（一）[67.5], 音頻電路設計[80.5], 離散數學[76.5,78.6], 類神經網路導論[84.6], 電機機械[69.5,63.8], 電能轉換實作專題[95.0], 系統級封裝設計實務[88.9], ＶＬＳＩ設計導論[81.2], 半導體元件（二）[84.1], 微電子技術[84.0], 最佳化簡介[81.0], 電源與電池管理系統導論[78.8]</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>微積分（一）[75.7], 微積分（一）[75.6], 微積分（一）[87.9], 計算機概論[77.1], 計算機概論[77.8], 計算機程式[77.3], 計算機程式[80.1], 計算機程式[80.4], 數位系統設計[83.9], 數位系統設計[64.5], 數位系統設計[81.5], 電工實驗（一）[74.1], 電工實驗（一）[74.8], 電子學（一）[65.3], 電子學（一）[65.6], 資料結構[77.2], 電路學（二）[76.2], 電路學（二）[67.5], 電力電子學[88.5], 電磁學（一）[76.8], 電磁學（一）[82.9], 訊號與系統[74.6], 訊號與系統[79.1], 硬體描述語言[85.7], 計算機組織[86.8], 電工實驗（三）[83.9], 電工實驗（三）[82.8], 電工實驗（五）[85.9], 電工實驗（五）[83.8], 電子學（三）[73.6], 半導體元件（一）[78.5], 奈微系統工程原理[82.0], 電子材料工程[79.9], 控制系統[67.3], 控制系統[66.8], 複變函數[73.4], 複變函數[75.6], 資料探勘導論[78.5], 電力系統（一）[83.3], 電機動態與控制[84.5], 工業配電[73.1], 微波工程[85.1], 通訊系統[70.4], 機器學習系統設計實務與應用[91.1], 數位訊號處理導論[68.8], 機率模式與應用[81.0]</t>
+          <t>微積分（一）[75.7,75.6,87.9], 計算機概論[77.1,77.8], 計算機程式[77.3,80.1,80.4], 數位系統設計[83.9,64.5,81.5], 電工實驗（一）[74.1,74.8], 電子學（一）[65.3,65.6], 資料結構[77.2], 電路學（二）[76.2,67.5], 電力電子學[88.5], 電磁學（一）[76.8,82.9], 訊號與系統[74.6,79.1], 硬體描述語言[85.7], 計算機組織[86.8], 電工實驗（三）[83.9,82.8], 電工實驗（五）[85.9,83.8], 電子學（三）[73.6], 半導體元件（一）[78.5], 奈微系統工程原理[82.0], 電子材料工程[79.9], 控制系統[67.3,66.8], 複變函數[73.4,75.6], 資料探勘導論[78.5], 電力系統（一）[83.3], 電機動態與控制[84.5], 工業配電[73.1], 微波工程[85.1], 通訊系統[70.4], 機器學習系統設計實務與應用[91.1], 數位訊號處理導論[68.8], 機率模式與應用[81.0]</t>
         </is>
       </c>
       <c r="C2" s="8" t="n">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>微積分（一）[75.7], 微積分（一）[75.6], 微積分（一）[87.9], 計算機概論[84.4], 計算機程式[77.3], 計算機程式[80.1], 計算機程式[80.4], 數位系統設計[83.9], 數位系統設計[64.5], 數位系統設計[81.5], 電工實驗（一）[74.1], 電工實驗（一）[74.8], 電子學（一）[65.3], 電子學（一）[65.6], 資料結構[77.2], 電路學（二）[76.2], 電路學（二）[67.5], 電力電子學[88.5], 電磁學（一）[76.8], 電磁學（一）[82.9], 訊號與系統[74.6], 訊號與系統[79.1], 硬體描述語言[85.7], 計算機組織[86.8], 電工實驗（三）[83.9], 電工實驗（三）[82.8], 電工實驗（五）[85.9], 電工實驗（五）[83.8], 電子學（三）[73.6], 半導體元件（一）[78.5], 奈微系統工程原理[82.0], 電子材料工程[79.9], 控制系統[67.3], 控制系統[66.8], 複變函數[73.4], 複變函數[75.6], 資料探勘導論[78.5], 電力系統（一）[83.3], 電機動態與控制[84.5], 工業配電[73.1], 微波工程[85.1], 通訊系統[70.4], 機器學習系統設計實務與應用[91.1], 數位訊號處理導論[68.8], 機率模式與應用[81.0]</t>
+          <t>微積分（一）[75.7,75.6,87.9], 計算機概論[84.4], 計算機程式[77.3,80.1,80.4], 數位系統設計[83.9,64.5,81.5], 電工實驗（一）[74.1,74.8], 電子學（一）[65.3,65.6], 資料結構[77.2], 電路學（二）[76.2,67.5], 電力電子學[88.5], 電磁學（一）[76.8,82.9], 訊號與系統[74.6,79.1], 硬體描述語言[85.7], 計算機組織[86.8], 電工實驗（三）[83.9,82.8], 電工實驗（五）[85.9,83.8], 電子學（三）[73.6], 半導體元件（一）[78.5], 奈微系統工程原理[82.0], 電子材料工程[79.9], 控制系統[67.3,66.8], 複變函數[73.4,75.6], 資料探勘導論[78.5], 電力系統（一）[83.3], 電機動態與控制[84.5], 工業配電[73.1], 微波工程[85.1], 通訊系統[70.4], 機器學習系統設計實務與應用[91.1], 數位訊號處理導論[68.8], 機率模式與應用[81.0]</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>微積分（一）[75.7], 微積分（一）[75.6], 微積分（一）[87.9], 計算機概論[77.1], 計算機概論[77.8], 計算機程式[77.3], 計算機程式[80.1], 計算機程式[80.4], 數位系統設計[83.9], 數位系統設計[64.5], 數位系統設計[81.5], 電工實驗（一）[74.1], 電工實驗（一）[74.8], 電子學（一）[65.3], 電子學（一）[65.6], 資料結構[77.2], 電路學（二）[76.2], 電路學（二）[67.5], 電力電子學[88.5], 訊號與系統[74.6], 計算機組織[86.8], 電工實驗（三）[83.9], 電工實驗（三）[82.8], 電工實驗（五）[83.8], 半導體元件（一）[78.5], 奈微系統工程原理[82.0], 控制系統[67.3], 資料探勘導論[78.5], 電力系統（一）[83.3], 工業配電[73.1], 通訊系統[70.4], 機器學習系統設計實務與應用[91.1]</t>
+          <t>微積分（一）[75.7,75.6,87.9], 計算機概論[77.1,77.8], 計算機程式[77.3,80.1,80.4], 數位系統設計[83.9,64.5,81.5], 電工實驗（一）[74.1,74.8], 電子學（一）[65.3,65.6], 資料結構[77.2], 電路學（二）[76.2,67.5], 電力電子學[88.5], 訊號與系統[74.6], 計算機組織[86.8], 電工實驗（三）[83.9,82.8], 電工實驗（五）[83.8], 半導體元件（一）[78.5], 奈微系統工程原理[82.0], 控制系統[67.3], 資料探勘導論[78.5], 電力系統（一）[83.3], 工業配電[73.1], 通訊系統[70.4], 機器學習系統設計實務與應用[91.1]</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>微積分（一）[75.7], 微積分（一）[75.6], 微積分（一）[87.9], 計算機程式[77.3], 計算機程式[80.1], 計算機程式[80.4], 數位系統設計[64.5], 數位系統設計[81.5], 電工實驗（一）[74.1], 電工實驗（一）[74.8], 電子學（一）[65.3], 電子學（一）[65.6], 資料結構[77.2], 電路學（二）[76.2], 硬體描述語言[85.7], 計算機組織[86.8], 電工實驗（三）[83.9], 電工實驗（五）[83.8], 電子學（三）[73.6], 奈微系統工程原理[82.0], 控制系統[67.3], 資料探勘導論[78.5], 電力系統（一）[83.3], 機器學習系統設計實務與應用[91.1], 機率模式與應用[81.0]</t>
+          <t>微積分（一）[75.7,75.6,87.9], 計算機程式[77.3,80.1,80.4], 數位系統設計[64.5,81.5], 電工實驗（一）[74.1,74.8], 電子學（一）[65.3,65.6], 資料結構[77.2], 電路學（二）[76.2], 硬體描述語言[85.7], 計算機組織[86.8], 電工實驗（三）[83.9], 電工實驗（五）[83.8], 電子學（三）[73.6], 奈微系統工程原理[82.0], 控制系統[67.3], 資料探勘導論[78.5], 電力系統（一）[83.3], 機器學習系統設計實務與應用[91.1], 機率模式與應用[81.0]</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>計算機概論[77.8], 計算機概論[84.4], 數位系統設計[64.5], 數位系統設計[81.5], 資料結構[77.2], 電子學（三）[73.6], 半導體元件（一）[78.5], 奈微系統工程原理[82.0], 電子材料工程[79.9], 控制系統[66.8], 電力系統（一）[83.3], 電機動態與控制[84.5], 通訊系統[70.4]</t>
+          <t>計算機概論[77.8,84.4], 數位系統設計[64.5,81.5], 資料結構[77.2], 電子學（三）[73.6], 半導體元件（一）[78.5], 奈微系統工程原理[82.0], 電子材料工程[79.9], 控制系統[66.8], 電力系統（一）[83.3], 電機動態與控制[84.5], 通訊系統[70.4]</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>微積分（二）[75.4], 微積分（二）[77.7], 微積分（二）[81.8], 微分方程[69.1], 微分方程[68.9], 微分方程[73.3], 電工實驗（二）[85.9], 電工實驗（二）[85.2], 電子學（二）[65.8], 電子學（二）[66.4], 線性代數[55.3], 線性代數[57.6], 線性代數[57.6], 電路學（一）[69.0], 電路學（一）[68.3], 電路學（一）[68.9], 嵌入式軟體設計[89.8], 化合物半導體概論[70.3], 音頻電路設計[90.3], 離散數學[83.0], 離散數學[83.2], 類神經網路導論[86.5], 電機機械[63.4], 電機機械[68.1], 電能轉換實作專題[84.0], 電磁學（二）[58.2], 電磁學（二）[69.2], 微波電路與系統模擬[95.0], 機率與統計[71.7], 機率與統計[72.4], 通訊系統模擬[88.9], ＶＬＳＩ設計導論[71.7], 實用數位系統設計[82.7], 以微控器為基礎之電路設計實務[85.6], 電工實驗（四）[82.3], 電工實驗（四）[79.6], 半導體元件（二）[81.7], 微電子技術[81.7], 電源與電池管理系統導論[82.9], 無線通訊系統導論[87.0], 通訊實作專題[89.4]</t>
+          <t>微積分（二）[75.4,77.7,81.8], 微分方程[69.1,68.9,73.3], 電工實驗（二）[85.9,85.2], 電子學（二）[65.8,66.4], 線性代數[55.3,57.6,57.6], 電路學（一）[69.0,68.3,68.9], 嵌入式軟體設計[89.8], 化合物半導體概論[70.3], 音頻電路設計[90.3], 離散數學[83.0,83.2], 類神經網路導論[86.5], 電機機械[63.4,68.1], 電能轉換實作專題[84.0], 電磁學（二）[58.2,69.2], 微波電路與系統模擬[95.0], 機率與統計[71.7,72.4], 通訊系統模擬[88.9], ＶＬＳＩ設計導論[71.7], 實用數位系統設計[82.7], 以微控器為基礎之電路設計實務[85.6], 電工實驗（四）[82.3,79.6], 半導體元件（二）[81.7], 微電子技術[81.7], 電源與電池管理系統導論[82.9], 無線通訊系統導論[87.0], 通訊實作專題[89.4]</t>
         </is>
       </c>
       <c r="C2" s="8" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>微積分（二）[75.4], 微積分（二）[77.7], 微積分（二）[81.8], 微分方程[69.1], 微分方程[68.9], 微分方程[73.3], 電工實驗（二）[85.9], 電工實驗（二）[85.2], 電子學（二）[65.8], 電子學（二）[66.4], 線性代數[55.3], 線性代數[57.6], 線性代數[57.6], 電路學（一）[69.0], 電路學（一）[68.3], 電路學（一）[68.9], 嵌入式軟體設計[89.8], 化合物半導體概論[70.3], 音頻電路設計[90.3], 離散數學[83.0], 離散數學[83.2], 類神經網路導論[86.5], 電機機械[63.4], 電機機械[68.1], 電能轉換實作專題[84.0], 電磁學（二）[58.2], 電磁學（二）[69.2], 微波電路與系統模擬[95.0], 機率與統計[71.7], 機率與統計[72.4], 通訊系統模擬[88.9], ＶＬＳＩ設計導論[71.7], 實用數位系統設計[82.7], 以微控器為基礎之電路設計實務[85.6], 電工實驗（四）[82.3], 電工實驗（四）[79.6], 半導體元件（二）[81.7], 微電子技術[81.7], 電源與電池管理系統導論[82.9], 無線通訊系統導論[87.0], 通訊實作專題[89.4]</t>
+          <t>微積分（二）[75.4,77.7,81.8], 微分方程[69.1,68.9,73.3], 電工實驗（二）[85.9,85.2], 電子學（二）[65.8,66.4], 線性代數[55.3,57.6,57.6], 電路學（一）[69.0,68.3,68.9], 嵌入式軟體設計[89.8], 化合物半導體概論[70.3], 音頻電路設計[90.3], 離散數學[83.0,83.2], 類神經網路導論[86.5], 電機機械[63.4,68.1], 電能轉換實作專題[84.0], 電磁學（二）[58.2,69.2], 微波電路與系統模擬[95.0], 機率與統計[71.7,72.4], 通訊系統模擬[88.9], ＶＬＳＩ設計導論[71.7], 實用數位系統設計[82.7], 以微控器為基礎之電路設計實務[85.6], 電工實驗（四）[82.3,79.6], 半導體元件（二）[81.7], 微電子技術[81.7], 電源與電池管理系統導論[82.9], 無線通訊系統導論[87.0], 通訊實作專題[89.4]</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>微積分（二）[75.4], 微積分（二）[77.7], 微積分（二）[81.8], 電工實驗（二）[85.9], 電工實驗（二）[85.2], 線性代數[55.3], 線性代數[57.6], 電路學（一）[69.0], 電路學（一）[68.3], 離散數學[83.0], 離散數學[83.2], 類神經網路導論[86.5], 電機機械[68.1], 電能轉換實作專題[84.0], ＶＬＳＩ設計導論[71.7], 實用數位系統設計[82.7], 電工實驗（四）[82.3], 電工實驗（四）[79.6], 半導體元件（二）[81.7], 微電子技術[81.7], 電源與電池管理系統導論[82.9], 通訊實作專題[89.4]</t>
+          <t>微積分（二）[75.4,77.7,81.8], 電工實驗（二）[85.9,85.2], 線性代數[55.3,57.6], 電路學（一）[69.0,68.3], 離散數學[83.0,83.2], 類神經網路導論[86.5], 電機機械[68.1], 電能轉換實作專題[84.0], ＶＬＳＩ設計導論[71.7], 實用數位系統設計[82.7], 電工實驗（四）[82.3,79.6], 半導體元件（二）[81.7], 微電子技術[81.7], 電源與電池管理系統導論[82.9], 通訊實作專題[89.4]</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>微積分（二）[77.7], 電子學（二）[65.8], 電子學（二）[66.4], 線性代數[57.6], 電路學（一）[69.0], 電路學（一）[68.3], 嵌入式軟體設計[89.8], 音頻電路設計[90.3], 類神經網路導論[86.5], 電機機械[63.4], 電機機械[68.1], 微波電路與系統模擬[95.0], 機率與統計[71.7], 機率與統計[72.4], 實用數位系統設計[82.7], 以微控器為基礎之電路設計實務[85.6], 電源與電池管理系統導論[82.9], 無線通訊系統導論[87.0]</t>
+          <t>微積分（二）[77.7], 電子學（二）[65.8,66.4], 線性代數[57.6], 電路學（一）[69.0,68.3], 嵌入式軟體設計[89.8], 音頻電路設計[90.3], 類神經網路導論[86.5], 電機機械[63.4,68.1], 微波電路與系統模擬[95.0], 機率與統計[71.7,72.4], 實用數位系統設計[82.7], 以微控器為基礎之電路設計實務[85.6], 電源與電池管理系統導論[82.9], 無線通訊系統導論[87.0]</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>微積分（二）[81.8], 電子學（二）[66.4], 線性代數[55.3], 電路學（一）[69.0], 音頻電路設計[90.3], 電機機械[63.4], 電機機械[68.1], 電能轉換實作專題[84.0], ＶＬＳＩ設計導論[71.7], 電工實驗（四）[82.3], 半導體元件（二）[81.7], 微電子技術[81.7], 電源與電池管理系統導論[82.9], 通訊實作專題[89.4]</t>
+          <t>微積分（二）[81.8], 電子學（二）[66.4], 線性代數[55.3], 電路學（一）[69.0], 音頻電路設計[90.3], 電機機械[63.4,68.1], 電能轉換實作專題[84.0], ＶＬＳＩ設計導論[71.7], 電工實驗（四）[82.3], 半導體元件（二）[81.7], 微電子技術[81.7], 電源與電池管理系統導論[82.9], 通訊實作專題[89.4]</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>計算機程式[84.1], 計算機程式[85.8], 計算機程式[77.4], 數位系統設計[73.4], 數位系統設計[70.8], 數位系統設計[67.6], 電工實驗（一）[76.5], 電工實驗（一）[75.4], 電工實驗（一）[80.1], 電子學（一）[65.2], 電子學（一）[78.0], 電子學（一）[81.8], 矩陣理論及應用[79.8], 資料結構[79.7], 資料結構[51.0], 電路學（二）[71.8], 電路學（二）[73.2], 電路學（二）[80.5], 電力電子學[78.0], 電力電子實驗[75.7], 電磁學（一）[75.8], 電磁學（一）[71.1], 電磁學（一）[71.9], 訊號與系統[77.8], 訊號與系統[73.6], 訊號與系統[80.3], 硬體描述語言[83.8], 電工實驗（三）[81.8], 電工實驗（三）[83.6], 電工實驗（五）[86.5], 電工實驗（五）[88.3], 電子學（三）[76.8], 半導體元件（一）[79.2], 奈微系統工程原理[79.7], 控制系統[71.3], 控制系統[64.0], 複變函數[80.0], 資料探勘導論[86.4], 電力系統（一）[79.8], 工程經濟[72.7], 微波工程[84.2], 無線功率傳輸系統[86.3], 微波放大器設計[95.0], 通訊系統[72.4], 通訊系統[77.4], 機器學習系統設計實務與應用[92.7], 數值運算實務[87.3], 數位訊號處理導論[87.6], 數位通訊[93.0], 機率模式與應用[66.8], 電機工程進階實作專案[89.5]</t>
+          <t>計算機程式[84.1,85.8,77.4], 數位系統設計[73.4,70.8,67.6], 電工實驗（一）[76.5,75.4,80.1], 電子學（一）[65.2,78.0,81.8], 矩陣理論及應用[79.8], 資料結構[79.7,51.0], 電路學（二）[71.8,73.2,80.5], 電力電子學[78.0], 電力電子實驗[75.7], 電磁學（一）[75.8,71.1,71.9], 訊號與系統[77.8,73.6,80.3], 硬體描述語言[83.8], 電工實驗（三）[81.8,83.6], 電工實驗（五）[86.5,88.3], 電子學（三）[76.8], 半導體元件（一）[79.2], 奈微系統工程原理[79.7], 控制系統[71.3,64.0], 複變函數[80.0], 資料探勘導論[86.4], 電力系統（一）[79.8], 工程經濟[72.7], 微波工程[84.2], 無線功率傳輸系統[86.3], 微波放大器設計[95.0], 通訊系統[72.4,77.4], 機器學習系統設計實務與應用[92.7], 數值運算實務[87.3], 數位訊號處理導論[87.6], 數位通訊[93.0], 機率模式與應用[66.8], 電機工程進階實作專案[89.5]</t>
         </is>
       </c>
       <c r="C2" s="8" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>微積分（一）[73.5], 計算機程式[84.1], 計算機程式[85.8], 計算機程式[77.4], 數位系統設計[73.4], 數位系統設計[70.8], 數位系統設計[67.6], 電工實驗（一）[76.5], 電工實驗（一）[75.4], 電工實驗（一）[80.1], 電子學（一）[65.2], 電子學（一）[78.0], 電子學（一）[81.8], 矩陣理論及應用[79.8], 資料結構[79.7], 資料結構[51.0], 電路學（二）[71.8], 電路學（二）[73.2], 電路學（二）[80.5], 電力電子學[78.0], 電力電子實驗[75.7], 電磁學（一）[75.8], 電磁學（一）[71.1], 電磁學（一）[71.9], 訊號與系統[77.8], 訊號與系統[73.6], 訊號與系統[80.3], 硬體描述語言[83.8], 電工實驗（三）[81.8], 電工實驗（三）[83.6], 電工實驗（五）[86.5], 電工實驗（五）[88.3], 電子學（三）[76.8], 半導體元件（一）[79.2], 奈微系統工程原理[79.7], 控制系統[71.3], 控制系統[64.0], 複變函數[80.0], 資料探勘導論[86.4], 電力系統（一）[79.8], 工程經濟[72.7], 微波工程[84.2], 無線功率傳輸系統[86.3], 微波放大器設計[95.0], 通訊系統[72.4], 通訊系統[77.4], 機器學習系統設計實務與應用[92.7], 數值運算實務[87.3], 數位訊號處理導論[87.6], 數位通訊[93.0], 機率模式與應用[66.8], 電機工程進階實作專案[89.5]</t>
+          <t>微積分（一）[73.5], 計算機程式[84.1,85.8,77.4], 數位系統設計[73.4,70.8,67.6], 電工實驗（一）[76.5,75.4,80.1], 電子學（一）[65.2,78.0,81.8], 矩陣理論及應用[79.8], 資料結構[79.7,51.0], 電路學（二）[71.8,73.2,80.5], 電力電子學[78.0], 電力電子實驗[75.7], 電磁學（一）[75.8,71.1,71.9], 訊號與系統[77.8,73.6,80.3], 硬體描述語言[83.8], 電工實驗（三）[81.8,83.6], 電工實驗（五）[86.5,88.3], 電子學（三）[76.8], 半導體元件（一）[79.2], 奈微系統工程原理[79.7], 控制系統[71.3,64.0], 複變函數[80.0], 資料探勘導論[86.4], 電力系統（一）[79.8], 工程經濟[72.7], 微波工程[84.2], 無線功率傳輸系統[86.3], 微波放大器設計[95.0], 通訊系統[72.4,77.4], 機器學習系統設計實務與應用[92.7], 數值運算實務[87.3], 數位訊號處理導論[87.6], 數位通訊[93.0], 機率模式與應用[66.8], 電機工程進階實作專案[89.5]</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>計算機程式[84.1], 計算機程式[85.8], 計算機程式[77.4], 數位系統設計[73.4], 數位系統設計[70.8], 數位系統設計[67.6], 電工實驗（一）[76.5], 電工實驗（一）[75.4], 電工實驗（一）[80.1], 電子學（一）[65.2], 電子學（一）[78.0], 電子學（一）[81.8], 資料結構[79.7], 資料結構[51.0], 電路學（二）[71.8], 電路學（二）[73.2], 電力電子學[78.0], 電力電子實驗[75.7], 硬體描述語言[83.8], 電工實驗（三）[81.8], 電工實驗（三）[83.6], 電工實驗（五）[86.5], 電工實驗（五）[88.3], 半導體元件（一）[79.2], 奈微系統工程原理[79.7], 控制系統[71.3], 資料探勘導論[86.4], 工程經濟[72.7], 微波放大器設計[95.0], 通訊系統[72.4], 機器學習系統設計實務與應用[92.7], 數值運算實務[87.3], 電機工程進階實作專案[89.5]</t>
+          <t>計算機程式[84.1,85.8,77.4], 數位系統設計[73.4,70.8,67.6], 電工實驗（一）[76.5,75.4,80.1], 電子學（一）[65.2,78.0,81.8], 資料結構[79.7,51.0], 電路學（二）[71.8,73.2], 電力電子學[78.0], 電力電子實驗[75.7], 硬體描述語言[83.8], 電工實驗（三）[81.8,83.6], 電工實驗（五）[86.5,88.3], 半導體元件（一）[79.2], 奈微系統工程原理[79.7], 控制系統[71.3], 資料探勘導論[86.4], 工程經濟[72.7], 微波放大器設計[95.0], 通訊系統[72.4], 機器學習系統設計實務與應用[92.7], 數值運算實務[87.3], 電機工程進階實作專案[89.5]</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>計算機概論[74.5], 計算機程式[84.1], 計算機程式[85.8], 計算機程式[77.4], 數位系統設計[73.4], 數位系統設計[70.8], 電子學（一）[65.2], 電子學（一）[78.0], 矩陣理論及應用[79.8], 資料結構[79.7], 資料結構[51.0], 電路學（二）[80.5], 電力電子實驗[75.7], 硬體描述語言[83.8], 電工實驗（三）[81.8], 電子學（三）[76.8], 控制系統[71.3], 電力系統（一）[79.8], 工程經濟[72.7], 無線功率傳輸系統[86.3], 微波放大器設計[95.0], 通訊系統[77.4], 機器學習系統設計實務與應用[92.7], 數值運算實務[87.3], 機率模式與應用[66.8], 電機工程進階實作專案[89.5]</t>
+          <t>計算機概論[74.5], 計算機程式[84.1,85.8,77.4], 數位系統設計[73.4,70.8], 電子學（一）[65.2,78.0], 矩陣理論及應用[79.8], 資料結構[79.7,51.0], 電路學（二）[80.5], 電力電子實驗[75.7], 硬體描述語言[83.8], 電工實驗（三）[81.8], 電子學（三）[76.8], 控制系統[71.3], 電力系統（一）[79.8], 工程經濟[72.7], 無線功率傳輸系統[86.3], 微波放大器設計[95.0], 通訊系統[77.4], 機器學習系統設計實務與應用[92.7], 數值運算實務[87.3], 機率模式與應用[66.8], 電機工程進階實作專案[89.5]</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>計算機概論[82.9], 計算機概論[82.4], 計算機概論[74.5], 數位系統設計[73.4], 數位系統設計[70.8], 數位系統設計[67.6], 電路學（二）[71.8], 電路學（二）[73.2], 電路學（二）[80.5], 電力電子實驗[75.7], 電工實驗（五）[88.3], 電子學（三）[76.8], 半導體元件（一）[79.2], 奈微系統工程原理[79.7], 控制系統[64.0], 資料探勘導論[86.4], 工程經濟[72.7], 無線功率傳輸系統[86.3], 通訊系統[72.4], 通訊系統[77.4], 數位通訊[93.0]</t>
+          <t>計算機概論[82.9,82.4,74.5], 數位系統設計[73.4,70.8,67.6], 電路學（二）[71.8,73.2,80.5], 電力電子實驗[75.7], 電工實驗（五）[88.3], 電子學（三）[76.8], 半導體元件（一）[79.2], 奈微系統工程原理[79.7], 控制系統[64.0], 資料探勘導論[86.4], 工程經濟[72.7], 無線功率傳輸系統[86.3], 通訊系統[72.4,77.4], 數位通訊[93.0]</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>微積分（二）[48.4], 微分方程[71.5], 微分方程[78.1], 微分方程[57.1], 電工實驗（二）[84.3], 電工實驗（二）[84.5], 電工實驗（二）[84.3], 電子學（二）[66.8], 電子學（二）[67.3], 電子學（二）[63.7], 線性代數[59.4], 線性代數[63.1], 線性代數[57.4], 電路學（一）[70.2], 電路學（一）[73.4], 嵌入式軟體設計[74.3], 計算機組織[74.8], 音頻電路設計[76.4], 作業系統[65.5], 離散數學[86.2], 離散數學[85.0], 類神經網路導論[88.3], 電機機械[66.3], 電機機械[59.1], 電機機械[82.0], 電磁學（二）[71.8], 電磁學（二）[70.3], 電磁學（二）[61.5], 微波元件導論[86.7], 微波電路與系統模擬[83.4], 機率與統計[67.5], 機率與統計[70.9], 機率與統計[69.5], 通訊系統模擬[88.8], ＶＬＳＩ設計導論[73.7], ＶＬＳＩ設計導論[78.1], 實用數位系統設計[78.6], 以微控器為基礎之電路設計實務[73.0], 生醫訊號處理與儀器實作專題[84.5], 電工實驗（四）[79.9], 電工實驗（四）[80.5], 半導體元件（二）[74.8], 微電子技術[77.0], 最佳控制簡介[87.0], 電子實作專題[89.7], 計算機實作專題[93.4], 計算機實作專題[85.9], 電力實作專題[85.8], 通訊實作專題[84.6], 通訊實作專題[86.3], 系統晶片實作專題[86.9], 系統晶片實作專題[87.8]</t>
+          <t>微積分（二）[48.4], 微分方程[71.5,78.1,57.1], 電工實驗（二）[84.3,84.5,84.3], 電子學（二）[66.8,67.3,63.7], 線性代數[59.4,63.1,57.4], 電路學（一）[70.2,73.4], 嵌入式軟體設計[74.3], 計算機組織[74.8], 音頻電路設計[76.4], 作業系統[65.5], 離散數學[86.2,85.0], 類神經網路導論[88.3], 電機機械[66.3,59.1,82.0], 電磁學（二）[71.8,70.3,61.5], 微波元件導論[86.7], 微波電路與系統模擬[83.4], 機率與統計[67.5,70.9,69.5], 通訊系統模擬[88.8], ＶＬＳＩ設計導論[73.7,78.1], 實用數位系統設計[78.6], 以微控器為基礎之電路設計實務[73.0], 生醫訊號處理與儀器實作專題[84.5], 電工實驗（四）[79.9,80.5], 半導體元件（二）[74.8], 微電子技術[77.0], 最佳控制簡介[87.0], 電子實作專題[89.7], 計算機實作專題[93.4,85.9], 電力實作專題[85.8], 通訊實作專題[84.6,86.3], 系統晶片實作專題[86.9,87.8]</t>
         </is>
       </c>
       <c r="C2" s="8" t="n">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>微積分（二）[68.3], 微積分（二）[69.7], 微積分（二）[48.4], 微分方程[71.5], 微分方程[78.1], 微分方程[57.1], 電工實驗（二）[84.3], 電工實驗（二）[84.5], 電工實驗（二）[84.3], 電子學（二）[66.8], 電子學（二）[67.3], 電子學（二）[63.7], 線性代數[59.4], 線性代數[63.1], 線性代數[57.4], 電路學（一）[70.2], 電路學（一）[73.4], 嵌入式軟體設計[74.3], 計算機組織[74.8], 音頻電路設計[76.4], 作業系統[65.5], 離散數學[86.2], 離散數學[85.0], 類神經網路導論[88.3], 電機機械[66.3], 電機機械[59.1], 電機機械[82.0], 電磁學（二）[61.5], 微波元件導論[86.7], 微波電路與系統模擬[83.4], 機率與統計[67.5], 機率與統計[70.9], 機率與統計[69.5], 通訊系統模擬[88.8], ＶＬＳＩ設計導論[73.7], ＶＬＳＩ設計導論[78.1], 實用數位系統設計[78.6], 以微控器為基礎之電路設計實務[73.0], 生醫訊號處理與儀器實作專題[84.5], 電工實驗（四）[79.9], 電工實驗（四）[80.5], 半導體元件（二）[74.8], 微電子技術[77.0], 最佳控制簡介[87.0], 電子實作專題[89.7], 計算機實作專題[93.4], 計算機實作專題[85.9], 電力實作專題[85.8], 通訊實作專題[84.6], 通訊實作專題[86.3], 系統晶片實作專題[86.9], 系統晶片實作專題[87.8]</t>
+          <t>微積分（二）[68.3,69.7,48.4], 微分方程[71.5,78.1,57.1], 電工實驗（二）[84.3,84.5,84.3], 電子學（二）[66.8,67.3,63.7], 線性代數[59.4,63.1,57.4], 電路學（一）[70.2,73.4], 嵌入式軟體設計[74.3], 計算機組織[74.8], 音頻電路設計[76.4], 作業系統[65.5], 離散數學[86.2,85.0], 類神經網路導論[88.3], 電機機械[66.3,59.1,82.0], 電磁學（二）[61.5], 微波元件導論[86.7], 微波電路與系統模擬[83.4], 機率與統計[67.5,70.9,69.5], 通訊系統模擬[88.8], ＶＬＳＩ設計導論[73.7,78.1], 實用數位系統設計[78.6], 以微控器為基礎之電路設計實務[73.0], 生醫訊號處理與儀器實作專題[84.5], 電工實驗（四）[79.9,80.5], 半導體元件（二）[74.8], 微電子技術[77.0], 最佳控制簡介[87.0], 電子實作專題[89.7], 計算機實作專題[93.4,85.9], 電力實作專題[85.8], 通訊實作專題[84.6,86.3], 系統晶片實作專題[86.9,87.8]</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>微分方程[71.5], 微分方程[57.1], 電工實驗（二）[84.3], 電工實驗（二）[84.5], 電工實驗（二）[84.3], 線性代數[59.4], 線性代數[63.1], 計算機組織[74.8], 作業系統[65.5], 離散數學[86.2], 離散數學[85.0], 類神經網路導論[88.3], 電機機械[59.1], 機率與統計[69.5], ＶＬＳＩ設計導論[73.7], ＶＬＳＩ設計導論[78.1], 實用數位系統設計[78.6], 以微控器為基礎之電路設計實務[73.0], 生醫訊號處理與儀器實作專題[84.5], 電工實驗（四）[79.9], 電工實驗（四）[80.5], 半導體元件（二）[74.8], 微電子技術[77.0], 電子實作專題[89.7], 計算機實作專題[93.4], 計算機實作專題[85.9], 電力實作專題[85.8], 通訊實作專題[84.6], 通訊實作專題[86.3], 系統晶片實作專題[86.9], 系統晶片實作專題[87.8]</t>
+          <t>微分方程[71.5,57.1], 電工實驗（二）[84.3,84.5,84.3], 線性代數[59.4,63.1], 計算機組織[74.8], 作業系統[65.5], 離散數學[86.2,85.0], 類神經網路導論[88.3], 電機機械[59.1], 機率與統計[69.5], ＶＬＳＩ設計導論[73.7,78.1], 實用數位系統設計[78.6], 以微控器為基礎之電路設計實務[73.0], 生醫訊號處理與儀器實作專題[84.5], 電工實驗（四）[79.9,80.5], 半導體元件（二）[74.8], 微電子技術[77.0], 電子實作專題[89.7], 計算機實作專題[93.4,85.9], 電力實作專題[85.8], 通訊實作專題[84.6,86.3], 系統晶片實作專題[86.9,87.8]</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>微積分（二）[48.4], 電子學（二）[66.8], 電子學（二）[67.3], 線性代數[59.4], 電路學（一）[70.2], 嵌入式軟體設計[74.3], 計算機組織[74.8], 音頻電路設計[76.4], 離散數學[86.2], 離散數學[85.0], 電機機械[59.1], 電機機械[82.0], 微波電路與系統模擬[83.4], 機率與統計[67.5], 機率與統計[70.9], 機率與統計[69.5], 通訊系統模擬[88.8], 實用數位系統設計[78.6], 以微控器為基礎之電路設計實務[73.0], 電工實驗（四）[79.9], 電工實驗（四）[80.5], 最佳控制簡介[87.0]</t>
+          <t>微積分（二）[48.4], 電子學（二）[66.8,67.3], 線性代數[59.4], 電路學（一）[70.2], 嵌入式軟體設計[74.3], 計算機組織[74.8], 音頻電路設計[76.4], 離散數學[86.2,85.0], 電機機械[59.1,82.0], 微波電路與系統模擬[83.4], 機率與統計[67.5,70.9,69.5], 通訊系統模擬[88.8], 實用數位系統設計[78.6], 以微控器為基礎之電路設計實務[73.0], 電工實驗（四）[79.9,80.5], 最佳控制簡介[87.0]</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>電子學（二）[67.3], 線性代數[59.4], 線性代數[63.1], 嵌入式軟體設計[74.3], 音頻電路設計[76.4], 類神經網路導論[88.3], 電機機械[66.3], 電機機械[59.1], 電機機械[82.0], ＶＬＳＩ設計導論[73.7], ＶＬＳＩ設計導論[78.1], 半導體元件（二）[74.8], 微電子技術[77.0]</t>
+          <t>電子學（二）[67.3], 線性代數[59.4,63.1], 嵌入式軟體設計[74.3], 音頻電路設計[76.4], 類神經網路導論[88.3], 電機機械[66.3,59.1,82.0], ＶＬＳＩ設計導論[73.7,78.1], 半導體元件（二）[74.8], 微電子技術[77.0]</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>微積分（一）[82.3], 微積分（一）[79.4], 微積分（一）[82.1], 計算機概論[77.8], 計算機程式[82.6], 計算機程式[80.7], 計算機程式[78.3], 數位系統設計[74.9], 數位系統設計[71.4], 數位系統設計[65.8], 電工實驗（一）[80.3], 電工實驗（一）[77.6], 電工實驗（一）[72.3], 電子學（一）[77.4], 電子學（一）[71.7], 電子學（一）[63.1], 矩陣理論及應用[80.2], 資料結構[69.3], 電路學（二）[68.3], 電路學（二）[71.5], 電路學（二）[55.6], 電力電子學[89.2], 電力電子學[78.9], 電磁學（一）[88.4], 電磁學（一）[90.3], 電磁學（一）[51.2], 訊號與系統[77.7], 訊號與系統[78.2], 訊號與系統[76.2], 硬體描述語言[84.8], 硬體描述語言[58.7], 電工實驗（三）[86.8], 電工實驗（三）[80.6], 電工實驗（三）[77.7], 電工實驗（五）[85.0], 電工實驗（五）[87.6], 電子學（三）[75.0], 半導體元件（一）[77.2], 奈微系統工程原理[78.1], 電子材料工程[78.0], 控制系統[71.3], 控制系統[68.4], 控制系統[61.3], 複變函數[78.0], 複變函數[20.0], 類神經網路導論[92.8], 電力系統（一）[71.5], 電力系統（一）[72.3], 微波工程[88.9], 微波放大器設計[95.0], 通訊系統[74.2], 通訊系統[73.8], 通訊系統[82.4], 多軸動感平台體感控制[88.4], 實用數位系統設計[80.2], 數位訊號處理導論[64.2], 機率模式與應用[84.5], 生醫工程導論[68.0], 電機工程進階實作專案[86.1]</t>
+          <t>微積分（一）[82.3,79.4,82.1], 計算機概論[77.8], 計算機程式[82.6,80.7,78.3], 數位系統設計[74.9,71.4,65.8], 電工實驗（一）[80.3,77.6,72.3], 電子學（一）[77.4,71.7,63.1], 矩陣理論及應用[80.2], 資料結構[69.3], 電路學（二）[68.3,71.5,55.6], 電力電子學[89.2,78.9], 電磁學（一）[88.4,90.3,51.2], 訊號與系統[77.7,78.2,76.2], 硬體描述語言[84.8,58.7], 電工實驗（三）[86.8,80.6,77.7], 電工實驗（五）[85.0,87.6], 電子學（三）[75.0], 半導體元件（一）[77.2], 奈微系統工程原理[78.1], 電子材料工程[78.0], 控制系統[71.3,68.4,61.3], 複變函數[78.0,20.0], 類神經網路導論[92.8], 電力系統（一）[71.5,72.3], 微波工程[88.9], 微波放大器設計[95.0], 通訊系統[74.2,73.8,82.4], 多軸動感平台體感控制[88.4], 實用數位系統設計[80.2], 數位訊號處理導論[64.2], 機率模式與應用[84.5], 生醫工程導論[68.0], 電機工程進階實作專案[86.1]</t>
         </is>
       </c>
       <c r="C2" s="8" t="n">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>微積分（一）[82.3], 微積分（一）[79.4], 計算機概論[77.8], 計算機程式[82.6], 計算機程式[80.7], 計算機程式[78.3], 數位系統設計[74.9], 數位系統設計[71.4], 數位系統設計[65.8], 電工實驗（一）[80.3], 電工實驗（一）[77.6], 電工實驗（一）[72.3], 電子學（一）[77.4], 電子學（一）[71.7], 電子學（一）[63.1], 矩陣理論及應用[80.2], 資料結構[69.3], 電路學（二）[68.3], 電路學（二）[71.5], 電路學（二）[55.6], 電力電子學[89.2], 電力電子學[78.9], 電磁學（一）[88.4], 電磁學（一）[90.3], 電磁學（一）[51.2], 訊號與系統[77.7], 訊號與系統[78.2], 訊號與系統[76.2], 硬體描述語言[84.8], 硬體描述語言[58.7], 電工實驗（三）[86.8], 電工實驗（三）[80.6], 電工實驗（三）[77.7], 電工實驗（五）[85.0], 電工實驗（五）[87.6], 電子學（三）[75.0], 半導體元件（一）[77.2], 奈微系統工程原理[78.1], 電子材料工程[78.0], 控制系統[71.3], 控制系統[68.4], 控制系統[61.3], 複變函數[78.0], 複變函數[20.0], 類神經網路導論[92.8], 電力系統（一）[71.5], 電力系統（一）[72.3], 微波工程[88.9], 微波放大器設計[95.0], 通訊系統[74.2], 通訊系統[73.8], 通訊系統[82.4], 多軸動感平台體感控制[88.4], 實用數位系統設計[80.2], 數位訊號處理導論[64.2], 機率模式與應用[84.5], 生醫工程導論[68.0], 電機工程進階實作專案[86.1]</t>
+          <t>微積分（一）[82.3,79.4], 計算機概論[77.8], 計算機程式[82.6,80.7,78.3], 數位系統設計[74.9,71.4,65.8], 電工實驗（一）[80.3,77.6,72.3], 電子學（一）[77.4,71.7,63.1], 矩陣理論及應用[80.2], 資料結構[69.3], 電路學（二）[68.3,71.5,55.6], 電力電子學[89.2,78.9], 電磁學（一）[88.4,90.3,51.2], 訊號與系統[77.7,78.2,76.2], 硬體描述語言[84.8,58.7], 電工實驗（三）[86.8,80.6,77.7], 電工實驗（五）[85.0,87.6], 電子學（三）[75.0], 半導體元件（一）[77.2], 奈微系統工程原理[78.1], 電子材料工程[78.0], 控制系統[71.3,68.4,61.3], 複變函數[78.0,20.0], 類神經網路導論[92.8], 電力系統（一）[71.5,72.3], 微波工程[88.9], 微波放大器設計[95.0], 通訊系統[74.2,73.8,82.4], 多軸動感平台體感控制[88.4], 實用數位系統設計[80.2], 數位訊號處理導論[64.2], 機率模式與應用[84.5], 生醫工程導論[68.0], 電機工程進階實作專案[86.1]</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>微積分（一）[82.3], 微積分（一）[79.4], 計算機概論[77.8], 計算機程式[82.6], 計算機程式[80.7], 計算機程式[78.3], 數位系統設計[74.9], 數位系統設計[71.4], 數位系統設計[65.8], 電工實驗（一）[80.3], 電工實驗（一）[77.6], 電工實驗（一）[72.3], 電子學（一）[71.7], 電子學（一）[63.1], 資料結構[69.3], 電路學（二）[68.3], 電路學（二）[71.5], 電力電子學[89.2], 硬體描述語言[84.8], 硬體描述語言[58.7], 電工實驗（三）[86.8], 電工實驗（三）[80.6], 電工實驗（三）[77.7], 電工實驗（五）[85.0], 電工實驗（五）[87.6], 半導體元件（一）[77.2], 奈微系統工程原理[78.1], 類神經網路導論[92.8], 微波放大器設計[95.0], 通訊系統[74.2], 通訊系統[73.8], 通訊系統[82.4], 多軸動感平台體感控制[88.4], 實用數位系統設計[80.2], 電機工程進階實作專案[86.1]</t>
+          <t>微積分（一）[82.3,79.4], 計算機概論[77.8], 計算機程式[82.6,80.7,78.3], 數位系統設計[74.9,71.4,65.8], 電工實驗（一）[80.3,77.6,72.3], 電子學（一）[71.7,63.1], 資料結構[69.3], 電路學（二）[68.3,71.5], 電力電子學[89.2], 硬體描述語言[84.8,58.7], 電工實驗（三）[86.8,80.6,77.7], 電工實驗（五）[85.0,87.6], 半導體元件（一）[77.2], 奈微系統工程原理[78.1], 類神經網路導論[92.8], 微波放大器設計[95.0], 通訊系統[74.2,73.8,82.4], 多軸動感平台體感控制[88.4], 實用數位系統設計[80.2], 電機工程進階實作專案[86.1]</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>微積分（一）[82.3], 微積分（一）[79.4], 計算機程式[82.6], 計算機程式[80.7], 計算機程式[78.3], 數位系統設計[74.9], 數位系統設計[71.4], 電子學（一）[77.4], 電子學（一）[71.7], 矩陣理論及應用[80.2], 資料結構[69.3], 電路學（二）[55.6], 電力電子學[78.9], 硬體描述語言[84.8], 電工實驗（三）[86.8], 電子學（三）[75.0], 類神經網路導論[92.8], 電力系統（一）[71.5], 電力系統（一）[72.3], 微波放大器設計[95.0], 多軸動感平台體感控制[88.4], 實用數位系統設計[80.2], 機率模式與應用[84.5], 電機工程進階實作專案[86.1]</t>
+          <t>微積分（一）[82.3,79.4], 計算機程式[82.6,80.7,78.3], 數位系統設計[74.9,71.4], 電子學（一）[77.4,71.7], 矩陣理論及應用[80.2], 資料結構[69.3], 電路學（二）[55.6], 電力電子學[78.9], 硬體描述語言[84.8], 電工實驗（三）[86.8], 電子學（三）[75.0], 類神經網路導論[92.8], 電力系統（一）[71.5,72.3], 微波放大器設計[95.0], 多軸動感平台體感控制[88.4], 實用數位系統設計[80.2], 機率模式與應用[84.5], 電機工程進階實作專案[86.1]</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>計算機概論[92.4], 計算機概論[90.5], 數位系統設計[74.9], 數位系統設計[71.4], 數位系統設計[65.8], 電路學（二）[68.3], 電路學（二）[71.5], 電路學（二）[55.6], 電力電子學[78.9], 電工實驗（五）[87.6], 電子學（三）[75.0], 半導體元件（一）[77.2], 奈微系統工程原理[78.1], 電子材料工程[78.0], 控制系統[71.3], 控制系統[68.4], 通訊系統[74.2], 通訊系統[73.8], 通訊系統[82.4], 生醫工程導論[68.0]</t>
+          <t>計算機概論[92.4,90.5], 數位系統設計[74.9,71.4,65.8], 電路學（二）[68.3,71.5,55.6], 電力電子學[78.9], 電工實驗（五）[87.6], 電子學（三）[75.0], 半導體元件（一）[77.2], 奈微系統工程原理[78.1], 電子材料工程[78.0], 控制系統[71.3,68.4], 通訊系統[74.2,73.8,82.4], 生醫工程導論[68.0]</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>微積分（二）[87.9], 微積分（二）[88.5], 微分方程[75.6], 微分方程[77.7], 微分方程[66.4], 電工實驗（二）[88.4], 電工實驗（二）[91.4], 電工實驗（二）[81.1], 電子學（二）[65.5], 電子學（二）[69.3], 電子學（二）[65.5], 線性代數[62.8], 線性代數[56.9], 線性代數[51.0], 電路學（一）[65.5], 電路學（一）[66.6], 嵌入式軟體設計[95.0], 計算機組織[86.5], 化合物半導體概論[82.5], 音頻電路設計[77.9], 離散數學[87.5], 離散數學[89.0], 離散數學[74.8], 電機機械[66.9], 電機機械[56.1], 電機機械[83.9], 電磁學（二）[69.7], 電磁學（二）[78.9], 電磁學（二）[60.2], 微波元件導論[88.4], 機率與統計[82.1], 機率與統計[75.8], 機率與統計[69.6], 通訊系統模擬[94.7], ＶＬＳＩ設計導論[91.0], ＶＬＳＩ設計導論[78.6], 實用數位系統設計[84.9], 機器學習系統設計實務與應用[93.5], 生醫訊號處理與儀器實作專題[92.3], 生醫訊號處理與儀器實作專題[95.0], 生醫訊號處理與儀器實作專題[74.2], 電工實驗（四）[77.0], 電工實驗（四）[75.1], 電工實驗（四）[81.0], 半導體元件（二）[83.8], 微電子技術[73.3], 微電子技術[82.1], 電子實作專題[90.7], 電子實作專題[70.6], 電子實作專題[95.0], 控制實作專題[87.0], 計算機實作專題[84.4], 計算機實作專題[95.0], 計算機實作專題[90.0], 電力實作專題[88.3], 電波與光電實作專題[82.0], 電波與光電實作專題[87.0], 電波與光電實作專題[87.0], 通訊實作專題[88.3], 通訊實作專題[92.9], 通訊實作專題[87.0], 系統晶片實作專題[85.1], 系統晶片實作專題[89.4], 系統晶片實作專題[85.2]</t>
+          <t>微積分（二）[87.9,88.5], 微分方程[75.6,77.7,66.4], 電工實驗（二）[88.4,91.4,81.1], 電子學（二）[65.5,69.3,65.5], 線性代數[62.8,56.9,51.0], 電路學（一）[65.5,66.6], 嵌入式軟體設計[95.0], 計算機組織[86.5], 化合物半導體概論[82.5], 音頻電路設計[77.9], 離散數學[87.5,89.0,74.8], 電機機械[66.9,56.1,83.9], 電磁學（二）[69.7,78.9,60.2], 微波元件導論[88.4], 機率與統計[82.1,75.8,69.6], 通訊系統模擬[94.7], ＶＬＳＩ設計導論[91.0,78.6], 實用數位系統設計[84.9], 機器學習系統設計實務與應用[93.5], 生醫訊號處理與儀器實作專題[92.3,95.0,74.2], 電工實驗（四）[77.0,75.1,81.0], 半導體元件（二）[83.8], 微電子技術[73.3,82.1], 電子實作專題[90.7,70.6,95.0], 控制實作專題[87.0], 計算機實作專題[84.4,95.0,90.0], 電力實作專題[88.3], 電波與光電實作專題[82.0,87.0,87.0], 通訊實作專題[88.3,92.9,87.0], 系統晶片實作專題[85.1,89.4,85.2]</t>
         </is>
       </c>
       <c r="C2" s="8" t="n">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>微積分（二）[87.9], 微積分（二）[88.5], 微積分（二）[80.7], 微分方程[75.6], 微分方程[77.7], 微分方程[66.4], 電工實驗（二）[88.4], 電工實驗（二）[91.4], 電工實驗（二）[81.1], 電子學（二）[65.5], 電子學（二）[69.3], 電子學（二）[65.5], 線性代數[62.8], 線性代數[56.9], 線性代數[51.0], 電路學（一）[65.5], 電路學（一）[66.6], 嵌入式軟體設計[95.0], 計算機組織[86.5], 化合物半導體概論[82.5], 音頻電路設計[77.9], 離散數學[87.5], 離散數學[89.0], 離散數學[74.8], 電機機械[66.9], 電機機械[56.1], 電機機械[83.9], 電磁學（二）[60.2], 微波元件導論[88.4], 機率與統計[82.1], 機率與統計[75.8], 機率與統計[69.6], 通訊系統模擬[94.7], ＶＬＳＩ設計導論[91.0], ＶＬＳＩ設計導論[78.6], 實用數位系統設計[84.9], 機器學習系統設計實務與應用[93.5], 生醫訊號處理與儀器實作專題[92.3], 生醫訊號處理與儀器實作專題[95.0], 生醫訊號處理與儀器實作專題[74.2], 電工實驗（四）[77.0], 電工實驗（四）[75.1], 電工實驗（四）[81.0], 半導體元件（二）[83.8], 微電子技術[73.3], 微電子技術[82.1], 電子實作專題[90.7], 電子實作專題[70.6], 電子實作專題[95.0], 控制實作專題[87.0], 計算機實作專題[84.4], 計算機實作專題[95.0], 計算機實作專題[90.0], 電力實作專題[88.3], 電波與光電實作專題[82.0], 電波與光電實作專題[87.0], 電波與光電實作專題[87.0], 通訊實作專題[88.3], 通訊實作專題[92.9], 通訊實作專題[87.0], 系統晶片實作專題[85.1], 系統晶片實作專題[89.4], 系統晶片實作專題[85.2]</t>
+          <t>微積分（二）[87.9,88.5,80.7], 微分方程[75.6,77.7,66.4], 電工實驗（二）[88.4,91.4,81.1], 電子學（二）[65.5,69.3,65.5], 線性代數[62.8,56.9,51.0], 電路學（一）[65.5,66.6], 嵌入式軟體設計[95.0], 計算機組織[86.5], 化合物半導體概論[82.5], 音頻電路設計[77.9], 離散數學[87.5,89.0,74.8], 電機機械[66.9,56.1,83.9], 電磁學（二）[60.2], 微波元件導論[88.4], 機率與統計[82.1,75.8,69.6], 通訊系統模擬[94.7], ＶＬＳＩ設計導論[91.0,78.6], 實用數位系統設計[84.9], 機器學習系統設計實務與應用[93.5], 生醫訊號處理與儀器實作專題[92.3,95.0,74.2], 電工實驗（四）[77.0,75.1,81.0], 半導體元件（二）[83.8], 微電子技術[73.3,82.1], 電子實作專題[90.7,70.6,95.0], 控制實作專題[87.0], 計算機實作專題[84.4,95.0,90.0], 電力實作專題[88.3], 電波與光電實作專題[82.0,87.0,87.0], 通訊實作專題[88.3,92.9,87.0], 系統晶片實作專題[85.1,89.4,85.2]</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>微積分（二）[87.9], 微積分（二）[88.5], 微分方程[75.6], 微分方程[66.4], 電工實驗（二）[88.4], 電工實驗（二）[91.4], 電工實驗（二）[81.1], 線性代數[62.8], 線性代數[56.9], 電路學（一）[65.5], 電路學（一）[66.6], 嵌入式軟體設計[95.0], 計算機組織[86.5], 離散數學[87.5], 離散數學[89.0], 離散數學[74.8], 電機機械[66.9], 電機機械[56.1], 電磁學（二）[69.7], 電磁學（二）[78.9], 機率與統計[69.6], ＶＬＳＩ設計導論[91.0], ＶＬＳＩ設計導論[78.6], 實用數位系統設計[84.9], 機器學習系統設計實務與應用[93.5], 生醫訊號處理與儀器實作專題[92.3], 生醫訊號處理與儀器實作專題[95.0], 生醫訊號處理與儀器實作專題[74.2], 電工實驗（四）[77.0], 電工實驗（四）[75.1], 電工實驗（四）[81.0], 半導體元件（二）[83.8], 微電子技術[73.3], 電子實作專題[90.7], 電子實作專題[70.6], 電子實作專題[95.0], 控制實作專題[87.0], 計算機實作專題[84.4], 計算機實作專題[95.0], 計算機實作專題[90.0], 電力實作專題[88.3], 電波與光電實作專題[82.0], 電波與光電實作專題[87.0], 電波與光電實作專題[87.0], 通訊實作專題[88.3], 通訊實作專題[92.9], 通訊實作專題[87.0], 系統晶片實作專題[85.1], 系統晶片實作專題[89.4], 系統晶片實作專題[85.2]</t>
+          <t>微積分（二）[87.9,88.5], 微分方程[75.6,66.4], 電工實驗（二）[88.4,91.4,81.1], 線性代數[62.8,56.9], 電路學（一）[65.5,66.6], 嵌入式軟體設計[95.0], 計算機組織[86.5], 離散數學[87.5,89.0,74.8], 電機機械[66.9,56.1], 電磁學（二）[69.7,78.9], 機率與統計[69.6], ＶＬＳＩ設計導論[91.0,78.6], 實用數位系統設計[84.9], 機器學習系統設計實務與應用[93.5], 生醫訊號處理與儀器實作專題[92.3,95.0,74.2], 電工實驗（四）[77.0,75.1,81.0], 半導體元件（二）[83.8], 微電子技術[73.3], 電子實作專題[90.7,70.6,95.0], 控制實作專題[87.0], 計算機實作專題[84.4,95.0,90.0], 電力實作專題[88.3], 電波與光電實作專題[82.0,87.0,87.0], 通訊實作專題[88.3,92.9,87.0], 系統晶片實作專題[85.1,89.4,85.2]</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>電子學（二）[65.5], 電子學（二）[69.3], 線性代數[62.8], 線性代數[56.9], 線性代數[51.0], 電路學（一）[65.5], 電路學（一）[66.6], 嵌入式軟體設計[95.0], 計算機組織[86.5], 音頻電路設計[77.9], 離散數學[87.5], 離散數學[89.0], 離散數學[74.8], 電機機械[66.9], 電機機械[56.1], 電機機械[83.9], 機率與統計[82.1], 機率與統計[75.8], 機率與統計[69.6], 通訊系統模擬[94.7], 實用數位系統設計[84.9], 機器學習系統設計實務與應用[93.5], 電工實驗（四）[77.0], 電工實驗（四）[75.1], 電工實驗（四）[81.0]</t>
+          <t>電子學（二）[65.5,69.3], 線性代數[62.8,56.9,51.0], 電路學（一）[65.5,66.6], 嵌入式軟體設計[95.0], 計算機組織[86.5], 音頻電路設計[77.9], 離散數學[87.5,89.0,74.8], 電機機械[66.9,56.1,83.9], 機率與統計[82.1,75.8,69.6], 通訊系統模擬[94.7], 實用數位系統設計[84.9], 機器學習系統設計實務與應用[93.5], 電工實驗（四）[77.0,75.1,81.0]</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>電子學（二）[69.3], 音頻電路設計[77.9], 電機機械[66.9], 電機機械[56.1], 電機機械[83.9], ＶＬＳＩ設計導論[91.0], ＶＬＳＩ設計導論[78.6], 半導體元件（二）[83.8], 微電子技術[73.3]</t>
+          <t>電子學（二）[69.3], 音頻電路設計[77.9], 電機機械[66.9,56.1,83.9], ＶＬＳＩ設計導論[91.0,78.6], 半導體元件（二）[83.8], 微電子技術[73.3]</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
